--- a/results/CB/Corrections.xlsx
+++ b/results/CB/Corrections.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M309"/>
+  <dimension ref="A1:M308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2778,7 +2778,11 @@
       <c r="E39" t="n">
         <v>6</v>
       </c>
-      <c r="F39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="G39" t="n">
         <v>9.49</v>
       </c>
@@ -2832,7 +2836,11 @@
           <t>dougie</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>M</t>
@@ -2955,7 +2963,11 @@
       <c r="E42" t="n">
         <v>19</v>
       </c>
-      <c r="F42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="G42" t="n">
         <v>11.08</v>
       </c>
@@ -3208,7 +3220,11 @@
           <t>GO</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>Experiment_2023-10-11T10:26:14.965471_atom_8_Test Type 1.log</t>
@@ -4607,7 +4623,11 @@
           <t>GO</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T13:01:26.435669_clover_nan_Training - fixed.log</t>
@@ -4664,7 +4684,11 @@
           <t>GO</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J70" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T13:01:26.435669_clover_nan_Training - fixed.log</t>
@@ -4721,7 +4745,11 @@
           <t>GO</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J71" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T13:01:26.435669_clover_nan_Training - fixed.log</t>
@@ -4778,7 +4806,11 @@
           <t>GO</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T13:01:26.435669_clover_nan_Training - fixed.log</t>
@@ -4835,7 +4867,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J73" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T13:01:26.435669_clover_nan_Training - fixed.log</t>
@@ -4892,7 +4928,11 @@
           <t>GO</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J74" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T13:01:26.435669_clover_nan_Training - fixed.log</t>
@@ -4949,7 +4989,11 @@
           <t>GO</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J75" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T13:01:26.435669_clover_nan_Training - fixed.log</t>
@@ -5006,7 +5050,11 @@
           <t>GO</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T13:01:26.435669_clover_nan_Training - fixed.log</t>
@@ -5063,7 +5111,11 @@
           <t>GO</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J77" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T13:01:26.435669_clover_nan_Training - fixed.log</t>
@@ -5120,7 +5172,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T13:01:26.435669_clover_nan_Training - fixed.log</t>
@@ -5177,7 +5233,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J79" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T13:01:26.435669_clover_nan_Training - fixed.log</t>
@@ -5234,7 +5294,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J80" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T13:01:26.435669_clover_nan_Training - fixed.log</t>
@@ -5291,7 +5355,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J81" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T13:01:26.435669_clover_nan_Training - fixed.log</t>
@@ -5348,7 +5416,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J82" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T13:01:26.435669_clover_nan_Training - fixed.log</t>
@@ -5405,7 +5477,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J83" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T13:01:26.435669_clover_nan_Training - fixed.log</t>
@@ -5462,7 +5538,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J84" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T13:01:26.435669_clover_nan_Training - fixed.log</t>
@@ -5519,7 +5599,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J85" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T13:01:26.435669_clover_nan_Training - fixed.log</t>
@@ -5576,7 +5660,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J86" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T13:01:26.435669_clover_nan_Training - fixed.log</t>
@@ -5633,7 +5721,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J87" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T13:01:26.435669_clover_nan_Training - fixed.log</t>
@@ -5812,7 +5904,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J90" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T18:03:46.698927_dusty_3.0_Training randomised Type 1.log</t>
@@ -5869,7 +5965,11 @@
           <t>GO</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J91" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T18:03:46.698927_dusty_3.0_Training randomised Type 1.log</t>
@@ -5926,7 +6026,11 @@
           <t>GO</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J92" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T18:03:46.698927_dusty_3.0_Training randomised Type 1.log</t>
@@ -5983,7 +6087,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J93" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T18:03:46.698927_dusty_3.0_Training randomised Type 1.log</t>
@@ -6040,7 +6148,11 @@
           <t>GO</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J94" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T18:03:46.698927_dusty_3.0_Training randomised Type 1.log</t>
@@ -6097,7 +6209,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J95" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T18:03:46.698927_dusty_3.0_Training randomised Type 1.log</t>
@@ -6154,7 +6270,11 @@
           <t>GO</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J96" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T18:03:46.698927_dusty_3.0_Training randomised Type 1.log</t>
@@ -6211,7 +6331,11 @@
           <t>GO</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J97" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T18:03:46.698927_dusty_3.0_Training randomised Type 1.log</t>
@@ -6268,7 +6392,11 @@
           <t>GO</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J98" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T18:03:46.698927_dusty_3.0_Training randomised Type 1.log</t>
@@ -6325,7 +6453,11 @@
           <t>GO</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J99" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T18:03:46.698927_dusty_3.0_Training randomised Type 1.log</t>
@@ -6382,7 +6514,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J100" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T18:03:46.698927_dusty_3.0_Training randomised Type 1.log</t>
@@ -6561,7 +6697,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J103" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T00:45:14.508317_myrtle_4.0_Training randomised Type 2.log</t>
@@ -6735,7 +6875,11 @@
       <c r="G106" t="n">
         <v>9.35</v>
       </c>
-      <c r="H106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="I106" t="inlineStr">
         <is>
           <t>No button press- resp is criterion</t>
@@ -6782,7 +6926,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -6790,16 +6934,16 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>9.69</v>
+        <v>9.15</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Horse released late</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -6819,7 +6963,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>GO, 9.69</t>
+          <t>, 9.15</t>
         </is>
       </c>
     </row>
@@ -6843,18 +6987,26 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>9.15</v>
-      </c>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
+        <v>9.01</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J108" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T04:07:06.316598_gio_4.0_Training randomised Type 2.log</t>
@@ -6872,7 +7024,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>, 9.15</t>
+          <t>, 9.01</t>
         </is>
       </c>
     </row>
@@ -6896,18 +7048,26 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>9.01</v>
-      </c>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
+        <v>8.949999999999999</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J109" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T04:07:06.316598_gio_4.0_Training randomised Type 2.log</t>
@@ -6925,7 +7085,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>, 9.01</t>
+          <t>, 8.95</t>
         </is>
       </c>
     </row>
@@ -6949,18 +7109,26 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T04:07:06.316598_gio_4.0_Training randomised Type 2.log</t>
@@ -6978,7 +7146,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>, 8.95</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7170,7 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -7017,7 +7185,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J111" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T04:07:06.316598_gio_4.0_Training randomised Type 2.log</t>
@@ -7059,22 +7231,26 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>30</v>
+        <v>8.69</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J112" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T04:07:06.316598_gio_4.0_Training randomised Type 2.log</t>
@@ -7092,7 +7268,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>, 8.69</t>
         </is>
       </c>
     </row>
@@ -7116,18 +7292,26 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>8.69</v>
-      </c>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J113" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T04:07:06.316598_gio_4.0_Training randomised Type 2.log</t>
@@ -7145,7 +7329,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>, 8.69</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -7169,7 +7353,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -7184,7 +7368,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T04:07:06.316598_gio_4.0_Training randomised Type 2.log</t>
@@ -7226,22 +7414,26 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>30</v>
+        <v>9.09</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T04:07:06.316598_gio_4.0_Training randomised Type 2.log</t>
@@ -7259,7 +7451,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>, 9.09</t>
         </is>
       </c>
     </row>
@@ -7283,18 +7475,26 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J116" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T04:07:06.316598_gio_4.0_Training randomised Type 2.log</t>
@@ -7312,7 +7512,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>, 9.09</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -7336,22 +7536,26 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>30</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J117" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T04:07:06.316598_gio_4.0_Training randomised Type 2.log</t>
@@ -7369,7 +7573,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>, 9.13</t>
         </is>
       </c>
     </row>
@@ -7380,20 +7584,20 @@
         </is>
       </c>
       <c r="B118" s="2" t="n">
-        <v>45248</v>
+        <v>45249</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>CBR2</t>
+          <t>CBR3</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>gio</t>
+          <t>myrtle</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -7401,13 +7605,21 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>9.130000000000001</v>
-      </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
+        <v>10.68</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Late button press for GO</t>
+        </is>
+      </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-14T04:07:06.316598_gio_4.0_Training randomised Type 2.log</t>
+          <t>Experiment_2023-11-14T10:23:47.643202_myrtle_6.0_Training randomised Type 1.log</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7422,7 +7634,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>, 9.13</t>
+          <t>GO, 10.68</t>
         </is>
       </c>
     </row>
@@ -7433,42 +7645,42 @@
         </is>
       </c>
       <c r="B119" s="2" t="n">
-        <v>45249</v>
+        <v>45248</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>CBR3</t>
+          <t>CBR2</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>myrtle</t>
+          <t>dusty</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>10.68</v>
+        <v>30</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Late button press for GO</t>
+          <t>Go response triggered but NoGo</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-14T10:23:47.643202_myrtle_6.0_Training randomised Type 1.log</t>
+          <t>Experiment_2023-11-14T12:13:40.543722_dusty_6.0_Training randomised Type 1.log</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7483,7 +7695,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>GO, 10.68</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -7507,24 +7719,24 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>30</v>
+        <v>12.4</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Go response triggered but NoGo</t>
+          <t>Early horse release before button not pressed</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7544,7 +7756,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 12.4</t>
         </is>
       </c>
     </row>
@@ -7555,11 +7767,11 @@
         </is>
       </c>
       <c r="B121" s="2" t="n">
-        <v>45248</v>
+        <v>45249</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CBR2</t>
+          <t>CBR3</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -7568,7 +7780,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -7576,7 +7788,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>12.4</v>
+        <v>10.52</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -7585,7 +7797,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Early horse release before button not pressed</t>
+          <t>Late button press for GO</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7605,7 +7817,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>GO, 12.4</t>
+          <t>GO, 10.52</t>
         </is>
       </c>
     </row>
@@ -7620,16 +7832,16 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>CBR3</t>
+          <t>CBT1</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>dusty</t>
+          <t>gio</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -7637,7 +7849,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>10.52</v>
+        <v>10.22</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -7651,7 +7863,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-14T12:13:40.543722_dusty_6.0_Training randomised Type 1.log</t>
+          <t>Experiment_2023-11-14T12:37:30.469954_gio_5.0_Test Type 1.log</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -7666,7 +7878,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>GO, 10.52</t>
+          <t>GO, 10.22</t>
         </is>
       </c>
     </row>
@@ -7690,15 +7902,15 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>10.22</v>
+        <v>7.83</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -7707,7 +7919,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Late button press for GO</t>
+          <t>Go response triggered but Not registered</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -7727,7 +7939,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>GO, 10.22</t>
+          <t>GO, 7.83</t>
         </is>
       </c>
     </row>
@@ -7742,24 +7954,24 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>CBT1</t>
+          <t>CBR2</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>gio</t>
+          <t>pumba</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>7.83</v>
+        <v>12.04</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -7768,12 +7980,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Go response triggered but Not registered</t>
+          <t>NoGo response when should be Go response- no button press</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-14T12:37:30.469954_gio_5.0_Test Type 1.log</t>
+          <t>Experiment_2023-11-14T15:40:26.284336_pumba_nan_Training randomised Type 2.log</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -7788,7 +8000,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>GO, 7.83</t>
+          <t>GO, 12.04</t>
         </is>
       </c>
     </row>
@@ -7799,42 +8011,44 @@
         </is>
       </c>
       <c r="B125" s="2" t="n">
-        <v>45249</v>
+        <v>45250</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CBR2</t>
+          <t>CBT1</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>pumba</t>
+          <t>jelly</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="G125" t="n">
-        <v>12.04</v>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>NoGo response when should be Go response- no button press</t>
+          <t>NoGo response but ate from bucket</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-14T15:40:26.284336_pumba_nan_Training randomised Type 2.log</t>
+          <t>Experiment_2023-11-14T17:14:25.139579_jelly_6.0_Test Type 1.log</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -7849,7 +8063,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>GO, 12.04</t>
+          <t xml:space="preserve">, </t>
         </is>
       </c>
     </row>
@@ -7869,23 +8083,33 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>jelly</t>
+          <t>myrtle</t>
         </is>
       </c>
       <c r="E126" t="n">
         <v>1</v>
       </c>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>NoGo response but ate from bucket</t>
+          <t>Restart test CBT1 because wrong trial type ignore first POS bucket in CBT1 and use 1st response in previous session</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-14T17:14:25.139579_jelly_6.0_Test Type 1.log</t>
+          <t>Experiment_2023-11-14T18:48:28.476282_myrtle_8.0_Test Type 1.log</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -7900,7 +8124,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t xml:space="preserve">, </t>
+          <t>GO, 12.6</t>
         </is>
       </c>
     </row>
@@ -7915,24 +8139,24 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>CBT1</t>
+          <t>CBR3</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>myrtle</t>
+          <t>yoshi</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>12.6</v>
+        <v>9.68</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -7941,12 +8165,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Restart test CBT1 because wrong trial type ignore first POS bucket in CBT1 and use 1st response in previous session</t>
+          <t>Was neg. but bucket was positive-check vid- Go response</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-14T18:48:28.476282_myrtle_8.0_Test Type 1.log</t>
+          <t>Experiment_2023-11-14T19:16:58.918521_yoshi_6.0_Training randomised Type 1.log</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -7961,7 +8185,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>GO, 12.6</t>
+          <t>GO, 9.68</t>
         </is>
       </c>
     </row>
@@ -7985,24 +8209,24 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>9.68</v>
+        <v>30</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Was neg. but bucket was positive-check vid- Go response</t>
+          <t>?</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -8022,7 +8246,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>GO, 9.68</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -8046,11 +8270,11 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -8107,24 +8331,26 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G130" t="n">
-        <v>30</v>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>As per the sheet</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -8144,7 +8370,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t xml:space="preserve">, </t>
         </is>
       </c>
     </row>
@@ -8159,32 +8385,38 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>CBR3</t>
+          <t>CBT1</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>yoshi</t>
+          <t>freya</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
+      <c r="G131" t="n">
+        <v>30</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>NOGO</t>
+        </is>
+      </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>As per the sheet</t>
+          <t>Windy/rain storm, did not approach first Pos bucket</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-14T19:16:58.918521_yoshi_6.0_Training randomised Type 1.log</t>
+          <t>Experiment_2023-11-14T23:17:57.967289_freya_nan_Test Type 2.log</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -8199,7 +8431,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t xml:space="preserve">, </t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -8210,42 +8442,42 @@
         </is>
       </c>
       <c r="B132" s="2" t="n">
-        <v>45250</v>
+        <v>45251</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>CBT1</t>
+          <t>CBT2</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>freya</t>
+          <t>george</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>NN</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>30</v>
+        <v>15.45</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Windy/rain storm, did not approach first Pos bucket</t>
+          <t>Late button press for GO</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-14T23:17:57.967289_freya_nan_Test Type 2.log</t>
+          <t>Experiment_2023-11-15T02:59:50.231712_george_6.0_Test Type 2.log</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -8260,7 +8492,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 15.45</t>
         </is>
       </c>
     </row>
@@ -8280,19 +8512,19 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>george</t>
+          <t>nix</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>NN</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>15.45</v>
+        <v>10.27</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -8301,12 +8533,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Late button press for GO</t>
+          <t xml:space="preserve"> Errors in test- 7N + 5P</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-15T02:59:50.231712_george_6.0_Test Type 2.log</t>
+          <t>Experiment_2023-11-15T04:42:42.109160_nix_9.0_Test Type 1.log</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8321,7 +8553,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>GO, 15.45</t>
+          <t>GO, 10.27</t>
         </is>
       </c>
     </row>
@@ -8345,24 +8577,24 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>P</t>
+          <t xml:space="preserve">N </t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>10.27</v>
+        <v>30</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Errors in test- 7N + 5P</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8382,7 +8614,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>GO, 10.27</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -8406,22 +8638,26 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">N </t>
+          <t>M</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>30</v>
+        <v>9.15</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J135" t="inlineStr">
         <is>
           <t>Experiment_2023-11-15T04:42:42.109160_nix_9.0_Test Type 1.log</t>
@@ -8439,7 +8675,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 9.15</t>
         </is>
       </c>
     </row>
@@ -8463,22 +8699,26 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>M</t>
+          <t xml:space="preserve">N </t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>9.15</v>
+        <v>30</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Meant to be P</t>
+        </is>
+      </c>
       <c r="J136" t="inlineStr">
         <is>
           <t>Experiment_2023-11-15T04:42:42.109160_nix_9.0_Test Type 1.log</t>
@@ -8496,7 +8736,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>GO, 9.15</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -8520,24 +8760,24 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">N </t>
+          <t>P</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>30</v>
+        <v>9.81</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Meant to be P</t>
+          <t>Meant to be N</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -8557,7 +8797,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 9.81</t>
         </is>
       </c>
     </row>
@@ -8581,24 +8821,24 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>P</t>
+          <t xml:space="preserve">N </t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>9.81</v>
+        <v>30</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Meant to be N</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -8618,7 +8858,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>GO, 9.81</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -8642,11 +8882,11 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">N </t>
+          <t>N</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -8657,7 +8897,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Meant to be NP</t>
+        </is>
+      </c>
       <c r="J139" t="inlineStr">
         <is>
           <t>Experiment_2023-11-15T04:42:42.109160_nix_9.0_Test Type 1.log</t>
@@ -8699,24 +8943,24 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>30</v>
+        <v>9.74</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Meant to be NP</t>
+          <t>meant to be P</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -8736,7 +8980,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 9.74</t>
         </is>
       </c>
     </row>
@@ -8760,15 +9004,15 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>9.74</v>
+        <v>15.25</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -8777,7 +9021,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>meant to be P</t>
+          <t>Meant to be P</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -8797,7 +9041,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>GO, 9.74</t>
+          <t>GO, 15.25</t>
         </is>
       </c>
     </row>
@@ -8821,24 +9065,24 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>15.25</v>
+        <v>30</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Meant to be P</t>
+          <t>meant to be P</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -8858,7 +9102,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>GO, 15.25</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -8882,24 +9126,24 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>30</v>
+        <v>11.53</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>meant to be P</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -8919,7 +9163,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 11.53</t>
         </is>
       </c>
     </row>
@@ -8943,22 +9187,26 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>11.53</v>
+        <v>24.2</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J144" t="inlineStr">
         <is>
           <t>Experiment_2023-11-15T04:42:42.109160_nix_9.0_Test Type 1.log</t>
@@ -8976,7 +9224,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>GO, 11.53</t>
+          <t>GO, 24.2</t>
         </is>
       </c>
     </row>
@@ -9000,22 +9248,26 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>NN</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>24.2</v>
+        <v>30</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J145" t="inlineStr">
         <is>
           <t>Experiment_2023-11-15T04:42:42.109160_nix_9.0_Test Type 1.log</t>
@@ -9033,7 +9285,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>GO, 24.2</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -9057,22 +9309,26 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>NN</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>30</v>
+        <v>11.09</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J146" t="inlineStr">
         <is>
           <t>Experiment_2023-11-15T04:42:42.109160_nix_9.0_Test Type 1.log</t>
@@ -9090,7 +9346,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 11.09</t>
         </is>
       </c>
     </row>
@@ -9114,22 +9370,26 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>11.09</v>
+        <v>30</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J147" t="inlineStr">
         <is>
           <t>Experiment_2023-11-15T04:42:42.109160_nix_9.0_Test Type 1.log</t>
@@ -9147,7 +9407,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>GO, 11.09</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -9167,29 +9427,33 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>nix</t>
+          <t>gio</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>30</v>
+        <v>10.12</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Pos bucket on wrong side- late Go response due to wrong bucket side</t>
+        </is>
+      </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-15T04:42:42.109160_nix_9.0_Test Type 1.log</t>
+          <t>Experiment_2023-11-15T05:22:53.513691_gio_6.0_Test Type 2.log</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -9204,7 +9468,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 10.12</t>
         </is>
       </c>
     </row>
@@ -9228,7 +9492,7 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -9236,7 +9500,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>10.12</v>
+        <v>9.49</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -9245,7 +9509,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Pos bucket on wrong side- late Go response due to wrong bucket side</t>
+          <t>Go button pressed too early</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -9265,7 +9529,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>GO, 10.12</t>
+          <t>GO, 9.49</t>
         </is>
       </c>
     </row>
@@ -9276,7 +9540,7 @@
         </is>
       </c>
       <c r="B150" s="2" t="n">
-        <v>45251</v>
+        <v>45252</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -9285,19 +9549,19 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>gio</t>
+          <t>smudge</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G150" t="n">
-        <v>9.49</v>
+        <v>29.46</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -9306,12 +9570,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Go button pressed too early</t>
+          <t>Just timed out on Neg bucket for NoGo- check vid</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-15T05:22:53.513691_gio_6.0_Test Type 2.log</t>
+          <t>Experiment_2023-11-15T16:42:36.211643_smudge_8.0_Test Type 2.log</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -9326,7 +9590,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>GO, 9.49</t>
+          <t>GO, 29.46</t>
         </is>
       </c>
     </row>
@@ -9337,7 +9601,7 @@
         </is>
       </c>
       <c r="B151" s="2" t="n">
-        <v>45252</v>
+        <v>45253</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -9346,33 +9610,33 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>smudge</t>
+          <t>yoshi</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G151" t="n">
-        <v>29.46</v>
+        <v>10.93</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Just timed out on Neg bucket for NoGo- check vid</t>
+          <t>Early horse release before button not pressed</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-15T16:42:36.211643_smudge_8.0_Test Type 2.log</t>
+          <t>Experiment_2023-11-15T18:35:59.371714_yoshi_9.0_Test Type 2.log</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -9387,7 +9651,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>GO, 29.46</t>
+          <t>, 10.93</t>
         </is>
       </c>
     </row>
@@ -9407,11 +9671,11 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>yoshi</t>
+          <t>clover</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -9419,17 +9683,21 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>10.93</v>
-      </c>
-      <c r="H152" t="inlineStr"/>
+        <v>11.85</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Early horse release before button not pressed</t>
+          <t>Errors in test at trial 11 a N was run instead of a P.  An extra trial was added so horse did 16 trials</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-15T18:35:59.371714_yoshi_9.0_Test Type 2.log</t>
+          <t>Experiment_2023-11-15T23:18:27.463685_clover_nan_Test Type 2.log</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -9444,7 +9712,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>, 10.93</t>
+          <t>GO, 11.85</t>
         </is>
       </c>
     </row>
@@ -9468,15 +9736,15 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G153" t="n">
-        <v>11.85</v>
+        <v>18.88</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -9485,7 +9753,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Errors in test at trial 11 a N was run instead of a P.  An extra trial was added so horse did 16 trials</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -9505,7 +9773,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>GO, 11.85</t>
+          <t>GO, 18.88</t>
         </is>
       </c>
     </row>
@@ -9529,22 +9797,26 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G154" t="n">
-        <v>18.88</v>
+        <v>30</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J154" t="inlineStr">
         <is>
           <t>Experiment_2023-11-15T23:18:27.463685_clover_nan_Test Type 2.log</t>
@@ -9562,7 +9834,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>GO, 18.88</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -9586,22 +9858,26 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G155" t="n">
-        <v>30</v>
+        <v>10.94</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J155" t="inlineStr">
         <is>
           <t>Experiment_2023-11-15T23:18:27.463685_clover_nan_Test Type 2.log</t>
@@ -9619,7 +9895,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 10.94</t>
         </is>
       </c>
     </row>
@@ -9643,22 +9919,26 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G156" t="n">
-        <v>10.94</v>
+        <v>30</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J156" t="inlineStr">
         <is>
           <t>Experiment_2023-11-15T23:18:27.463685_clover_nan_Test Type 2.log</t>
@@ -9676,7 +9956,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>GO, 10.94</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -9700,7 +9980,7 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -9715,7 +9995,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr"/>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J157" t="inlineStr">
         <is>
           <t>Experiment_2023-11-15T23:18:27.463685_clover_nan_Test Type 2.log</t>
@@ -9757,11 +10041,11 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -9772,7 +10056,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr"/>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J158" t="inlineStr">
         <is>
           <t>Experiment_2023-11-15T23:18:27.463685_clover_nan_Test Type 2.log</t>
@@ -9814,22 +10102,26 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G159" t="n">
-        <v>30</v>
+        <v>11.93</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J159" t="inlineStr">
         <is>
           <t>Experiment_2023-11-15T23:18:27.463685_clover_nan_Test Type 2.log</t>
@@ -9847,7 +10139,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 11.93</t>
         </is>
       </c>
     </row>
@@ -9871,22 +10163,26 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G160" t="n">
-        <v>11.93</v>
+        <v>30</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J160" t="inlineStr">
         <is>
           <t>Experiment_2023-11-15T23:18:27.463685_clover_nan_Test Type 2.log</t>
@@ -9904,7 +10200,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>GO, 11.93</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -9928,22 +10224,26 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G161" t="n">
-        <v>30</v>
+        <v>10.48</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J161" t="inlineStr">
         <is>
           <t>Experiment_2023-11-15T23:18:27.463685_clover_nan_Test Type 2.log</t>
@@ -9961,7 +10261,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 10.48</t>
         </is>
       </c>
     </row>
@@ -9985,7 +10285,7 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -9993,14 +10293,18 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>10.48</v>
+        <v>12.67</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr"/>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Was run as N, then repeated so horse did extra 11 (P). </t>
+        </is>
+      </c>
       <c r="J162" t="inlineStr">
         <is>
           <t>Experiment_2023-11-15T23:18:27.463685_clover_nan_Test Type 2.log</t>
@@ -10018,7 +10322,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>GO, 10.48</t>
+          <t>GO, 12.67</t>
         </is>
       </c>
     </row>
@@ -10042,24 +10346,24 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G163" t="n">
-        <v>12.67</v>
+        <v>30</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Was run as N, then repeated so horse did extra 11 (P). </t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -10079,7 +10383,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>GO, 12.67</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -10103,11 +10407,11 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>NN</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -10118,7 +10422,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr"/>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J164" t="inlineStr">
         <is>
           <t>Experiment_2023-11-15T23:18:27.463685_clover_nan_Test Type 2.log</t>
@@ -10160,22 +10468,26 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>NN</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G165" t="n">
-        <v>30</v>
+        <v>12.8</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J165" t="inlineStr">
         <is>
           <t>Experiment_2023-11-15T23:18:27.463685_clover_nan_Test Type 2.log</t>
@@ -10193,7 +10505,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 12.8</t>
         </is>
       </c>
     </row>
@@ -10217,22 +10529,26 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G166" t="n">
-        <v>12.8</v>
+        <v>30</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J166" t="inlineStr">
         <is>
           <t>Experiment_2023-11-15T23:18:27.463685_clover_nan_Test Type 2.log</t>
@@ -10250,7 +10566,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>GO, 12.8</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -10261,38 +10577,42 @@
         </is>
       </c>
       <c r="B167" s="2" t="n">
-        <v>45253</v>
+        <v>45255</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>CBT2</t>
+          <t>CBT3</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>clover</t>
+          <t>nix</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G167" t="n">
-        <v>30</v>
+        <v>10.01</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Bucket on the wrong side</t>
+        </is>
+      </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-15T23:18:27.463685_clover_nan_Test Type 2.log</t>
+          <t>Experiment_2023-11-16T09:12:31.465402_nix_10.0_Test Type 3.log</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -10307,7 +10627,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 10.01</t>
         </is>
       </c>
     </row>
@@ -10331,24 +10651,24 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G168" t="n">
-        <v>10.01</v>
+        <v>30</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Bucket on the wrong side</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -10368,7 +10688,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>GO, 10.01</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -10392,22 +10712,26 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G169" t="n">
-        <v>30</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J169" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T09:12:31.465402_nix_10.0_Test Type 3.log</t>
@@ -10425,7 +10749,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 9.8</t>
         </is>
       </c>
     </row>
@@ -10449,22 +10773,26 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G170" t="n">
-        <v>9.800000000000001</v>
+        <v>20.87</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr"/>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J170" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T09:12:31.465402_nix_10.0_Test Type 3.log</t>
@@ -10482,7 +10810,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>GO, 9.8</t>
+          <t>GO, 20.87</t>
         </is>
       </c>
     </row>
@@ -10506,22 +10834,26 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G171" t="n">
-        <v>20.87</v>
+        <v>9.35</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr"/>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J171" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T09:12:31.465402_nix_10.0_Test Type 3.log</t>
@@ -10539,7 +10871,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>GO, 20.87</t>
+          <t>GO, 9.35</t>
         </is>
       </c>
     </row>
@@ -10563,22 +10895,26 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G172" t="n">
-        <v>9.35</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr"/>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J172" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T09:12:31.465402_nix_10.0_Test Type 3.log</t>
@@ -10596,7 +10932,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>GO, 9.35</t>
+          <t>GO, 8.95</t>
         </is>
       </c>
     </row>
@@ -10620,7 +10956,7 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -10628,14 +10964,18 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>8.949999999999999</v>
+        <v>10.57</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr"/>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Two buckets- check video</t>
+        </is>
+      </c>
       <c r="J173" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T09:12:31.465402_nix_10.0_Test Type 3.log</t>
@@ -10653,7 +10993,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>GO, 8.95</t>
+          <t>GO, 10.57</t>
         </is>
       </c>
     </row>
@@ -10677,24 +11017,24 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G174" t="n">
-        <v>10.57</v>
+        <v>30</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Two buckets- check video</t>
+          <t>Two buckets (extra trial?)</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -10714,7 +11054,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>GO, 10.57</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -10738,24 +11078,24 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G175" t="n">
-        <v>30</v>
+        <v>9.48</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Two buckets (extra trial?)</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -10775,7 +11115,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 9.48</t>
         </is>
       </c>
     </row>
@@ -10799,22 +11139,26 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G176" t="n">
-        <v>9.48</v>
+        <v>11.14</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr"/>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J176" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T09:12:31.465402_nix_10.0_Test Type 3.log</t>
@@ -10832,7 +11176,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>GO, 9.48</t>
+          <t>GO, 11.14</t>
         </is>
       </c>
     </row>
@@ -10856,22 +11200,26 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G177" t="n">
-        <v>11.14</v>
+        <v>30</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J177" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T09:12:31.465402_nix_10.0_Test Type 3.log</t>
@@ -10889,7 +11237,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>GO, 11.14</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -10913,7 +11261,7 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -10921,14 +11269,18 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>30</v>
+        <v>13.46</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J178" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T09:12:31.465402_nix_10.0_Test Type 3.log</t>
@@ -10946,7 +11298,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 13.46</t>
         </is>
       </c>
     </row>
@@ -10970,22 +11322,26 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G179" t="n">
-        <v>13.46</v>
+        <v>8.49</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr"/>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J179" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T09:12:31.465402_nix_10.0_Test Type 3.log</t>
@@ -11003,7 +11359,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>GO, 13.46</t>
+          <t>GO, 8.49</t>
         </is>
       </c>
     </row>
@@ -11027,22 +11383,26 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>NN</t>
         </is>
       </c>
       <c r="G180" t="n">
-        <v>8.49</v>
+        <v>30</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Did not touch. Bucket</t>
+        </is>
+      </c>
       <c r="J180" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T09:12:31.465402_nix_10.0_Test Type 3.log</t>
@@ -11060,7 +11420,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>GO, 8.49</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -11084,11 +11444,11 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>NN</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -11101,7 +11461,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Did not touch. Bucket</t>
+          <t>Early horse release before button not pressed</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -11132,11 +11492,11 @@
         </is>
       </c>
       <c r="B182" s="2" t="n">
-        <v>45255</v>
+        <v>45256</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>CBT3</t>
+          <t>CBT4</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -11145,29 +11505,29 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G182" t="n">
-        <v>30</v>
+        <v>11.01</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Early horse release before button not pressed</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-16T09:12:31.465402_nix_10.0_Test Type 3.log</t>
+          <t>Experiment_2023-11-16T15:46:42.899255_nix_11.0_Test Type 1.log</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -11182,7 +11542,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 11.01</t>
         </is>
       </c>
     </row>
@@ -11206,22 +11566,26 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G183" t="n">
-        <v>11.01</v>
+        <v>12.99</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr"/>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Late button press for GO</t>
+        </is>
+      </c>
       <c r="J183" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T15:46:42.899255_nix_11.0_Test Type 1.log</t>
@@ -11239,7 +11603,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>GO, 11.01</t>
+          <t>GO, 12.99</t>
         </is>
       </c>
     </row>
@@ -11263,15 +11627,15 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G184" t="n">
-        <v>12.99</v>
+        <v>10.07</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -11280,7 +11644,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Late button press for GO</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -11300,7 +11664,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>GO, 12.99</t>
+          <t>GO, 10.07</t>
         </is>
       </c>
     </row>
@@ -11324,22 +11688,26 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G185" t="n">
-        <v>10.07</v>
+        <v>12.67</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I185" t="inlineStr"/>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No button press- Go resp is criterion- check vids </t>
+        </is>
+      </c>
       <c r="J185" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T15:46:42.899255_nix_11.0_Test Type 1.log</t>
@@ -11357,7 +11725,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>GO, 10.07</t>
+          <t>GO, 12.67</t>
         </is>
       </c>
     </row>
@@ -11381,15 +11749,15 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G186" t="n">
-        <v>12.67</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -11398,7 +11766,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">No button press- Go resp is criterion- check vids </t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -11418,7 +11786,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>GO, 12.67</t>
+          <t>GO, 9.87</t>
         </is>
       </c>
     </row>
@@ -11442,7 +11810,7 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -11450,14 +11818,18 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>9.869999999999999</v>
+        <v>12.41</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I187" t="inlineStr"/>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J187" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T15:46:42.899255_nix_11.0_Test Type 1.log</t>
@@ -11475,7 +11847,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>GO, 9.87</t>
+          <t>GO, 12.41</t>
         </is>
       </c>
     </row>
@@ -11499,22 +11871,26 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G188" t="n">
-        <v>12.41</v>
+        <v>30</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J188" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T15:46:42.899255_nix_11.0_Test Type 1.log</t>
@@ -11532,7 +11908,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>GO, 12.41</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -11556,22 +11932,26 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G189" t="n">
-        <v>30</v>
+        <v>11.2</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J189" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T15:46:42.899255_nix_11.0_Test Type 1.log</t>
@@ -11589,7 +11969,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 11.2</t>
         </is>
       </c>
     </row>
@@ -11613,22 +11993,26 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G190" t="n">
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I190" t="inlineStr"/>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J190" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T15:46:42.899255_nix_11.0_Test Type 1.log</t>
@@ -11646,7 +12030,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>GO, 11.2</t>
+          <t>GO, 10.4</t>
         </is>
       </c>
     </row>
@@ -11670,22 +12054,26 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G191" t="n">
-        <v>10.4</v>
+        <v>30</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J191" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T15:46:42.899255_nix_11.0_Test Type 1.log</t>
@@ -11703,7 +12091,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>GO, 10.4</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -11727,7 +12115,7 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -11742,7 +12130,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I192" t="inlineStr"/>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J192" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T15:46:42.899255_nix_11.0_Test Type 1.log</t>
@@ -11784,22 +12176,26 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G193" t="n">
-        <v>30</v>
+        <v>10.2</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J193" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T15:46:42.899255_nix_11.0_Test Type 1.log</t>
@@ -11817,7 +12213,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 10.2</t>
         </is>
       </c>
     </row>
@@ -11841,22 +12237,26 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>NN</t>
         </is>
       </c>
       <c r="G194" t="n">
-        <v>10.2</v>
+        <v>30</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J194" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T15:46:42.899255_nix_11.0_Test Type 1.log</t>
@@ -11874,7 +12274,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>GO, 10.2</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -11898,22 +12298,26 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>NN</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G195" t="n">
-        <v>30</v>
+        <v>11.39</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J195" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T15:46:42.899255_nix_11.0_Test Type 1.log</t>
@@ -11931,7 +12335,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 11.39</t>
         </is>
       </c>
     </row>
@@ -11955,22 +12359,26 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G196" t="n">
-        <v>11.39</v>
+        <v>30</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J196" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T15:46:42.899255_nix_11.0_Test Type 1.log</t>
@@ -11988,7 +12396,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>GO, 11.39</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -12008,29 +12416,33 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>nix</t>
+          <t>gio</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G197" t="n">
-        <v>30</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>2 Log files, computer stopped after trial 3 Median- Restart trial 4?</t>
+        </is>
+      </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-16T15:46:42.899255_nix_11.0_Test Type 1.log</t>
+          <t>Experiment_2023-11-16T17:55:24.333022_gio_9.0_Test Type 1.log</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -12045,7 +12457,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 9.29</t>
         </is>
       </c>
     </row>
@@ -12069,24 +12481,24 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G198" t="n">
-        <v>9.289999999999999</v>
+        <v>30</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>2 Log files, computer stopped after trial 3 Median- Restart trial 4?</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -12106,7 +12518,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>GO, 9.29</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -12130,22 +12542,26 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G199" t="n">
-        <v>30</v>
+        <v>10.36</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J199" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T17:55:24.333022_gio_9.0_Test Type 1.log</t>
@@ -12163,7 +12579,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 10.36</t>
         </is>
       </c>
     </row>
@@ -12187,22 +12603,26 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G200" t="n">
-        <v>10.36</v>
+        <v>30</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J200" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T17:55:24.333022_gio_9.0_Test Type 1.log</t>
@@ -12220,7 +12640,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>GO, 10.36</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -12244,22 +12664,26 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G201" t="n">
-        <v>30</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J201" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T17:55:24.333022_gio_9.0_Test Type 1.log</t>
@@ -12277,7 +12701,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 9.87</t>
         </is>
       </c>
     </row>
@@ -12301,7 +12725,7 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -12309,14 +12733,18 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>9.869999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr"/>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J202" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T17:55:24.333022_gio_9.0_Test Type 1.log</t>
@@ -12334,7 +12762,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>GO, 9.87</t>
+          <t>GO, 9.33</t>
         </is>
       </c>
     </row>
@@ -12358,22 +12786,26 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G203" t="n">
-        <v>9.33</v>
+        <v>30</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J203" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T17:55:24.333022_gio_9.0_Test Type 1.log</t>
@@ -12391,7 +12823,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>GO, 9.33</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -12415,22 +12847,26 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G204" t="n">
-        <v>30</v>
+        <v>8.76</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J204" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T17:55:24.333022_gio_9.0_Test Type 1.log</t>
@@ -12448,7 +12884,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 8.76</t>
         </is>
       </c>
     </row>
@@ -12472,22 +12908,26 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G205" t="n">
-        <v>8.76</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr"/>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J205" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T17:55:24.333022_gio_9.0_Test Type 1.log</t>
@@ -12505,7 +12945,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>GO, 8.76</t>
+          <t>GO, 9.22</t>
         </is>
       </c>
     </row>
@@ -12529,22 +12969,26 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G206" t="n">
-        <v>9.220000000000001</v>
+        <v>30</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J206" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T17:55:24.333022_gio_9.0_Test Type 1.log</t>
@@ -12562,7 +13006,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>GO, 9.22</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -12586,7 +13030,7 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -12601,7 +13045,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr"/>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J207" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T17:55:24.333022_gio_9.0_Test Type 1.log</t>
@@ -12643,22 +13091,26 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G208" t="n">
-        <v>30</v>
+        <v>9.43</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J208" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T17:55:24.333022_gio_9.0_Test Type 1.log</t>
@@ -12676,7 +13128,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 9.43</t>
         </is>
       </c>
     </row>
@@ -12700,22 +13152,26 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>NN</t>
         </is>
       </c>
       <c r="G209" t="n">
-        <v>9.43</v>
+        <v>30</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J209" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T17:55:24.333022_gio_9.0_Test Type 1.log</t>
@@ -12733,7 +13189,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>GO, 9.43</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -12757,22 +13213,26 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>NN</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G210" t="n">
-        <v>30</v>
+        <v>9.66</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J210" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T17:55:24.333022_gio_9.0_Test Type 1.log</t>
@@ -12790,7 +13250,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 9.66</t>
         </is>
       </c>
     </row>
@@ -12814,22 +13274,26 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G211" t="n">
-        <v>9.66</v>
+        <v>30</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J211" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T17:55:24.333022_gio_9.0_Test Type 1.log</t>
@@ -12847,7 +13311,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>GO, 9.66</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -12858,7 +13322,7 @@
         </is>
       </c>
       <c r="B212" s="2" t="n">
-        <v>45256</v>
+        <v>45257</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -12867,11 +13331,11 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>gio</t>
+          <t>jelly</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -12879,17 +13343,21 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>30</v>
+        <v>27.17</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Go response but not captured </t>
+        </is>
+      </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-16T17:55:24.333022_gio_9.0_Test Type 1.log</t>
+          <t>Experiment_2023-11-16T19:24:59.492473_jelly_9.0_Test Type 1.log</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -12904,7 +13372,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 27.17</t>
         </is>
       </c>
     </row>
@@ -12928,15 +13396,15 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G213" t="n">
-        <v>27.17</v>
+        <v>11.2</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -12945,7 +13413,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Go response but not captured </t>
+          <t>late button press for GO due to broken robot</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -12965,7 +13433,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>GO, 27.17</t>
+          <t>GO, 11.2</t>
         </is>
       </c>
     </row>
@@ -12985,19 +13453,19 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>jelly</t>
+          <t>smudge</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G214" t="n">
-        <v>11.2</v>
+        <v>10.14</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -13006,12 +13474,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>late button press for GO due to broken robot</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-16T19:24:59.492473_jelly_9.0_Test Type 1.log</t>
+          <t>Experiment_2023-11-16T20:27:00.214523_smudge_10.0_Test Type 1.log</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -13026,7 +13494,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>GO, 11.2</t>
+          <t>GO, 10.14</t>
         </is>
       </c>
     </row>
@@ -13050,22 +13518,26 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G215" t="n">
-        <v>10.14</v>
+        <v>30</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J215" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T20:27:00.214523_smudge_10.0_Test Type 1.log</t>
@@ -13083,7 +13555,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>GO, 10.14</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -13107,22 +13579,26 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G216" t="n">
-        <v>30</v>
+        <v>10.79</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Go response but not captured </t>
+        </is>
+      </c>
       <c r="J216" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T20:27:00.214523_smudge_10.0_Test Type 1.log</t>
@@ -13140,7 +13616,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 10.79</t>
         </is>
       </c>
     </row>
@@ -13164,24 +13640,24 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G217" t="n">
-        <v>10.79</v>
+        <v>30</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Go response but not captured </t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -13201,7 +13677,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>GO, 10.79</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -13225,22 +13701,26 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G218" t="n">
-        <v>30</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J218" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T20:27:00.214523_smudge_10.0_Test Type 1.log</t>
@@ -13258,7 +13738,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 9.87</t>
         </is>
       </c>
     </row>
@@ -13282,7 +13762,7 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -13290,14 +13770,18 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>9.869999999999999</v>
+        <v>10.87</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I219" t="inlineStr"/>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J219" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T20:27:00.214523_smudge_10.0_Test Type 1.log</t>
@@ -13315,7 +13799,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>GO, 9.87</t>
+          <t>GO, 10.87</t>
         </is>
       </c>
     </row>
@@ -13339,22 +13823,26 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G220" t="n">
-        <v>10.87</v>
+        <v>30</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>NoGo response when should be Go response</t>
+        </is>
+      </c>
       <c r="J220" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T20:27:00.214523_smudge_10.0_Test Type 1.log</t>
@@ -13372,7 +13860,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>GO, 10.87</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -13396,24 +13884,24 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G221" t="n">
-        <v>30</v>
+        <v>10.13</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>NoGo response when should be Go response</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -13433,7 +13921,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 10.13</t>
         </is>
       </c>
     </row>
@@ -13457,22 +13945,26 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G222" t="n">
-        <v>10.13</v>
+        <v>10.22</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I222" t="inlineStr"/>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J222" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T20:27:00.214523_smudge_10.0_Test Type 1.log</t>
@@ -13490,7 +13982,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>GO, 10.13</t>
+          <t>GO, 10.22</t>
         </is>
       </c>
     </row>
@@ -13514,22 +14006,26 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G223" t="n">
-        <v>10.22</v>
+        <v>30</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J223" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T20:27:00.214523_smudge_10.0_Test Type 1.log</t>
@@ -13547,7 +14043,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>GO, 10.22</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -13571,7 +14067,7 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -13586,7 +14082,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I224" t="inlineStr"/>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J224" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T20:27:00.214523_smudge_10.0_Test Type 1.log</t>
@@ -13628,22 +14128,26 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G225" t="n">
-        <v>30</v>
+        <v>10.87</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Video and log don't match but NoGO is criterion</t>
+        </is>
+      </c>
       <c r="J225" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T20:27:00.214523_smudge_10.0_Test Type 1.log</t>
@@ -13661,7 +14165,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 10.87</t>
         </is>
       </c>
     </row>
@@ -13685,24 +14189,24 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>NN</t>
         </is>
       </c>
       <c r="G226" t="n">
-        <v>10.87</v>
+        <v>30</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Video and log don't match but NoGO is criterion</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -13722,7 +14226,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>GO, 10.87</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -13746,22 +14250,26 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>NN</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G227" t="n">
-        <v>30</v>
+        <v>10.87</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J227" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T20:27:00.214523_smudge_10.0_Test Type 1.log</t>
@@ -13779,7 +14287,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 10.87</t>
         </is>
       </c>
     </row>
@@ -13803,22 +14311,26 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G228" t="n">
-        <v>10.87</v>
+        <v>30</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J228" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T20:27:00.214523_smudge_10.0_Test Type 1.log</t>
@@ -13836,7 +14348,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>GO, 10.87</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -13851,34 +14363,38 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>CBT4</t>
+          <t>CBT3</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>smudge</t>
+          <t>myrtle</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G229" t="n">
-        <v>30</v>
+        <v>7.99</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-16T20:27:00.214523_smudge_10.0_Test Type 1.log</t>
+          <t>Experiment_2023-11-16T21:17:46.006067_myrtle_10.0_Test Type 3.log</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -13893,7 +14409,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 7.99</t>
         </is>
       </c>
     </row>
@@ -13917,22 +14433,26 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G230" t="n">
-        <v>7.99</v>
+        <v>30</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Go response triggered but NoGo</t>
+        </is>
+      </c>
       <c r="J230" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T21:17:46.006067_myrtle_10.0_Test Type 3.log</t>
@@ -13950,7 +14470,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>GO, 7.99</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -13974,24 +14494,24 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G231" t="n">
-        <v>30</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Go response triggered but NoGo</t>
+          <t>NoGo response when should be Go response</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -14011,7 +14531,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 9.14</t>
         </is>
       </c>
     </row>
@@ -14035,15 +14555,15 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G232" t="n">
-        <v>9.140000000000001</v>
+        <v>18.01</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -14052,7 +14572,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>NoGo response when should be Go response</t>
+          <t>OK on log-Nogo</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -14072,7 +14592,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>GO, 9.14</t>
+          <t>GO, 18.01</t>
         </is>
       </c>
     </row>
@@ -14096,15 +14616,15 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G233" t="n">
-        <v>18.01</v>
+        <v>10.56</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -14113,7 +14633,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>OK on log-Nogo</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -14133,7 +14653,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>GO, 18.01</t>
+          <t>GO, 10.56</t>
         </is>
       </c>
     </row>
@@ -14157,22 +14677,26 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G234" t="n">
-        <v>10.56</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I234" t="inlineStr"/>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Button pressed late?</t>
+        </is>
+      </c>
       <c r="J234" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T21:17:46.006067_myrtle_10.0_Test Type 3.log</t>
@@ -14190,7 +14714,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>GO, 10.56</t>
+          <t>GO, 9.22</t>
         </is>
       </c>
     </row>
@@ -14214,7 +14738,7 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -14222,7 +14746,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>9.220000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -14231,7 +14755,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Button pressed late?</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -14251,7 +14775,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>GO, 9.22</t>
+          <t>GO, 9.55</t>
         </is>
       </c>
     </row>
@@ -14275,22 +14799,26 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G236" t="n">
-        <v>9.550000000000001</v>
+        <v>30</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J236" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T21:17:46.006067_myrtle_10.0_Test Type 3.log</t>
@@ -14308,7 +14836,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>GO, 9.55</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -14332,11 +14860,11 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -14347,7 +14875,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I237" t="inlineStr"/>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J237" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T21:17:46.006067_myrtle_10.0_Test Type 3.log</t>
@@ -14389,22 +14921,26 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G238" t="n">
-        <v>30</v>
+        <v>10.13</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I238" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J238" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T21:17:46.006067_myrtle_10.0_Test Type 3.log</t>
@@ -14422,7 +14958,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 10.13</t>
         </is>
       </c>
     </row>
@@ -14446,22 +14982,26 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G239" t="n">
-        <v>10.13</v>
+        <v>30</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J239" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T21:17:46.006067_myrtle_10.0_Test Type 3.log</t>
@@ -14479,7 +15019,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>GO, 10.13</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -14503,7 +15043,7 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -14518,7 +15058,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I240" t="inlineStr"/>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J240" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T21:17:46.006067_myrtle_10.0_Test Type 3.log</t>
@@ -14560,22 +15104,26 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G241" t="n">
-        <v>30</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I241" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>OK on log-Nogo</t>
+        </is>
+      </c>
       <c r="J241" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T21:17:46.006067_myrtle_10.0_Test Type 3.log</t>
@@ -14593,7 +15141,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 9.63</t>
         </is>
       </c>
     </row>
@@ -14617,24 +15165,24 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>NN</t>
         </is>
       </c>
       <c r="G242" t="n">
-        <v>9.630000000000001</v>
+        <v>30</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>OK on log-Nogo</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -14654,7 +15202,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>GO, 9.63</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -14678,11 +15226,11 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>NN</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -14693,7 +15241,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I243" t="inlineStr"/>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J243" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T21:17:46.006067_myrtle_10.0_Test Type 3.log</t>
@@ -14731,29 +15283,33 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>myrtle</t>
+          <t>yoshi</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G244" t="n">
-        <v>30</v>
+        <v>8.23</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I244" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Late button press for GO</t>
+        </is>
+      </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-16T21:17:46.006067_myrtle_10.0_Test Type 3.log</t>
+          <t>Experiment_2023-11-16T22:01:25.798273_yoshi_10.0_Test Type 3.log</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -14768,7 +15324,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 8.23</t>
         </is>
       </c>
     </row>
@@ -14792,15 +15348,15 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G245" t="n">
-        <v>8.23</v>
+        <v>25.39</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -14809,7 +15365,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Late button press for GO</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -14829,7 +15385,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>GO, 8.23</t>
+          <t>GO, 25.39</t>
         </is>
       </c>
     </row>
@@ -14853,22 +15409,26 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G246" t="n">
-        <v>25.39</v>
+        <v>8.16</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I246" t="inlineStr"/>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J246" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T22:01:25.798273_yoshi_10.0_Test Type 3.log</t>
@@ -14886,7 +15446,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>GO, 25.39</t>
+          <t>GO, 8.16</t>
         </is>
       </c>
     </row>
@@ -14910,22 +15470,26 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G247" t="n">
-        <v>8.16</v>
+        <v>30</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I247" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J247" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T22:01:25.798273_yoshi_10.0_Test Type 3.log</t>
@@ -14943,7 +15507,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>GO, 8.16</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -14967,22 +15531,26 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G248" t="n">
-        <v>30</v>
+        <v>9.48</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I248" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J248" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T22:01:25.798273_yoshi_10.0_Test Type 3.log</t>
@@ -15000,7 +15568,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 9.48</t>
         </is>
       </c>
     </row>
@@ -15024,22 +15592,26 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G249" t="n">
-        <v>9.48</v>
+        <v>8.82</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I249" t="inlineStr"/>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J249" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T22:01:25.798273_yoshi_10.0_Test Type 3.log</t>
@@ -15057,7 +15629,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>GO, 9.48</t>
+          <t>GO, 8.82</t>
         </is>
       </c>
     </row>
@@ -15081,7 +15653,7 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -15089,14 +15661,18 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>8.82</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I250" t="inlineStr"/>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J250" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T22:01:25.798273_yoshi_10.0_Test Type 3.log</t>
@@ -15114,7 +15690,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>GO, 8.82</t>
+          <t>GO, 9.14</t>
         </is>
       </c>
     </row>
@@ -15138,22 +15714,26 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G251" t="n">
-        <v>9.140000000000001</v>
+        <v>30</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J251" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T22:01:25.798273_yoshi_10.0_Test Type 3.log</t>
@@ -15171,7 +15751,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>GO, 9.14</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -15195,22 +15775,26 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G252" t="n">
-        <v>30</v>
+        <v>8.6</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I252" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J252" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T22:01:25.798273_yoshi_10.0_Test Type 3.log</t>
@@ -15228,7 +15812,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 8.6</t>
         </is>
       </c>
     </row>
@@ -15252,22 +15836,26 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G253" t="n">
-        <v>8.6</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I253" t="inlineStr"/>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J253" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T22:01:25.798273_yoshi_10.0_Test Type 3.log</t>
@@ -15285,7 +15873,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>GO, 8.6</t>
+          <t>GO, 8.95</t>
         </is>
       </c>
     </row>
@@ -15309,22 +15897,26 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G254" t="n">
-        <v>8.949999999999999</v>
+        <v>30</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I254" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J254" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T22:01:25.798273_yoshi_10.0_Test Type 3.log</t>
@@ -15342,7 +15934,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>GO, 8.95</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -15366,7 +15958,7 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -15381,7 +15973,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I255" t="inlineStr"/>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J255" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T22:01:25.798273_yoshi_10.0_Test Type 3.log</t>
@@ -15423,22 +16019,26 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G256" t="n">
-        <v>30</v>
+        <v>9.08</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I256" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J256" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T22:01:25.798273_yoshi_10.0_Test Type 3.log</t>
@@ -15456,7 +16056,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 9.08</t>
         </is>
       </c>
     </row>
@@ -15480,22 +16080,26 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>NN</t>
         </is>
       </c>
       <c r="G257" t="n">
-        <v>9.08</v>
+        <v>30</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I257" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J257" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T22:01:25.798273_yoshi_10.0_Test Type 3.log</t>
@@ -15513,7 +16117,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>GO, 9.08</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -15537,11 +16141,11 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>NN</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -15552,7 +16156,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I258" t="inlineStr"/>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J258" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T22:01:25.798273_yoshi_10.0_Test Type 3.log</t>
@@ -15590,29 +16198,33 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>yoshi</t>
+          <t>dusty</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G259" t="n">
-        <v>30</v>
+        <v>7.62</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I259" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-16T22:01:25.798273_yoshi_10.0_Test Type 3.log</t>
+          <t>Experiment_2023-11-16T23:55:33.357304_dusty_9.0_Test Type 3.log</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -15627,7 +16239,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 7.62</t>
         </is>
       </c>
     </row>
@@ -15651,22 +16263,26 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G260" t="n">
-        <v>7.62</v>
+        <v>15.96</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I260" t="inlineStr"/>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J260" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T23:55:33.357304_dusty_9.0_Test Type 3.log</t>
@@ -15684,7 +16300,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>GO, 7.62</t>
+          <t>GO, 15.96</t>
         </is>
       </c>
     </row>
@@ -15708,22 +16324,26 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G261" t="n">
-        <v>15.96</v>
+        <v>8.56</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I261" t="inlineStr"/>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J261" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T23:55:33.357304_dusty_9.0_Test Type 3.log</t>
@@ -15741,7 +16361,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>GO, 15.96</t>
+          <t>GO, 8.56</t>
         </is>
       </c>
     </row>
@@ -15765,22 +16385,26 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G262" t="n">
-        <v>8.56</v>
+        <v>11.54</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I262" t="inlineStr"/>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J262" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T23:55:33.357304_dusty_9.0_Test Type 3.log</t>
@@ -15798,7 +16422,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>GO, 8.56</t>
+          <t>GO, 11.54</t>
         </is>
       </c>
     </row>
@@ -15822,22 +16446,26 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G263" t="n">
-        <v>11.54</v>
+        <v>30</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I263" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J263" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T23:55:33.357304_dusty_9.0_Test Type 3.log</t>
@@ -15855,7 +16483,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>GO, 11.54</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -15879,11 +16507,11 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -15894,7 +16522,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I264" t="inlineStr"/>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J264" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T23:55:33.357304_dusty_9.0_Test Type 3.log</t>
@@ -15936,7 +16568,7 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -15944,14 +16576,18 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>30</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I265" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J265" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T23:55:33.357304_dusty_9.0_Test Type 3.log</t>
@@ -15969,7 +16605,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 8.61</t>
         </is>
       </c>
     </row>
@@ -15993,22 +16629,26 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G266" t="n">
-        <v>8.609999999999999</v>
+        <v>30</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I266" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J266" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T23:55:33.357304_dusty_9.0_Test Type 3.log</t>
@@ -16026,7 +16666,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>GO, 8.61</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -16050,11 +16690,11 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -16065,7 +16705,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I267" t="inlineStr"/>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J267" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T23:55:33.357304_dusty_9.0_Test Type 3.log</t>
@@ -16107,22 +16751,26 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G268" t="n">
-        <v>30</v>
+        <v>9.6</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I268" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J268" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T23:55:33.357304_dusty_9.0_Test Type 3.log</t>
@@ -16140,7 +16788,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 9.6</t>
         </is>
       </c>
     </row>
@@ -16164,22 +16812,26 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G269" t="n">
-        <v>9.6</v>
+        <v>30</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I269" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J269" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T23:55:33.357304_dusty_9.0_Test Type 3.log</t>
@@ -16197,7 +16849,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>GO, 9.6</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -16221,7 +16873,7 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -16236,7 +16888,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I270" t="inlineStr"/>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J270" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T23:55:33.357304_dusty_9.0_Test Type 3.log</t>
@@ -16278,22 +16934,26 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G271" t="n">
-        <v>30</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I271" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J271" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T23:55:33.357304_dusty_9.0_Test Type 3.log</t>
@@ -16311,7 +16971,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 8.46</t>
         </is>
       </c>
     </row>
@@ -16335,22 +16995,26 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>NN</t>
         </is>
       </c>
       <c r="G272" t="n">
-        <v>8.460000000000001</v>
+        <v>30</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I272" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J272" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T23:55:33.357304_dusty_9.0_Test Type 3.log</t>
@@ -16368,7 +17032,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>GO, 8.46</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -16392,11 +17056,11 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>NN</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -16407,7 +17071,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I273" t="inlineStr"/>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J273" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T23:55:33.357304_dusty_9.0_Test Type 3.log</t>
@@ -16436,11 +17104,11 @@
         </is>
       </c>
       <c r="B274" s="2" t="n">
-        <v>45257</v>
+        <v>45258</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>CBT3</t>
+          <t>CBT4</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -16449,25 +17117,29 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G274" t="n">
-        <v>30</v>
+        <v>10.12</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I274" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-16T23:55:33.357304_dusty_9.0_Test Type 3.log</t>
+          <t>Experiment_2023-11-17T04:05:53.213724_dusty_10.0_Test Type 1.log</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
@@ -16482,7 +17154,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 10.12</t>
         </is>
       </c>
     </row>
@@ -16506,22 +17178,26 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G275" t="n">
-        <v>10.12</v>
+        <v>19.18</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I275" t="inlineStr"/>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J275" t="inlineStr">
         <is>
           <t>Experiment_2023-11-17T04:05:53.213724_dusty_10.0_Test Type 1.log</t>
@@ -16539,7 +17215,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>GO, 10.12</t>
+          <t>GO, 19.18</t>
         </is>
       </c>
     </row>
@@ -16563,22 +17239,26 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G276" t="n">
-        <v>19.18</v>
+        <v>30</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I276" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J276" t="inlineStr">
         <is>
           <t>Experiment_2023-11-17T04:05:53.213724_dusty_10.0_Test Type 1.log</t>
@@ -16596,7 +17276,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>GO, 19.18</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -16620,11 +17300,11 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -16635,7 +17315,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I277" t="inlineStr"/>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J277" t="inlineStr">
         <is>
           <t>Experiment_2023-11-17T04:05:53.213724_dusty_10.0_Test Type 1.log</t>
@@ -16677,22 +17361,26 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G278" t="n">
-        <v>30</v>
+        <v>9.92</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I278" t="inlineStr"/>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J278" t="inlineStr">
         <is>
           <t>Experiment_2023-11-17T04:05:53.213724_dusty_10.0_Test Type 1.log</t>
@@ -16710,7 +17398,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 9.92</t>
         </is>
       </c>
     </row>
@@ -16734,7 +17422,7 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -16742,14 +17430,18 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>9.92</v>
+        <v>9.49</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I279" t="inlineStr"/>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J279" t="inlineStr">
         <is>
           <t>Experiment_2023-11-17T04:05:53.213724_dusty_10.0_Test Type 1.log</t>
@@ -16767,7 +17459,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>GO, 9.92</t>
+          <t>GO, 9.49</t>
         </is>
       </c>
     </row>
@@ -16791,22 +17483,26 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G280" t="n">
-        <v>9.49</v>
+        <v>30</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I280" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J280" t="inlineStr">
         <is>
           <t>Experiment_2023-11-17T04:05:53.213724_dusty_10.0_Test Type 1.log</t>
@@ -16824,7 +17520,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>GO, 9.49</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -16848,11 +17544,11 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -16863,7 +17559,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I281" t="inlineStr"/>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J281" t="inlineStr">
         <is>
           <t>Experiment_2023-11-17T04:05:53.213724_dusty_10.0_Test Type 1.log</t>
@@ -16905,11 +17605,11 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -16920,7 +17620,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I282" t="inlineStr"/>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Bucket on the wrong side- was N, should have been P</t>
+        </is>
+      </c>
       <c r="J282" t="inlineStr">
         <is>
           <t>Experiment_2023-11-17T04:05:53.213724_dusty_10.0_Test Type 1.log</t>
@@ -16962,24 +17666,24 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G283" t="n">
-        <v>30</v>
+        <v>19.61</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>Bucket on the wrong side- was N, should have been P</t>
+          <t>Bucket on the wrong side was P, should have been N</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
@@ -16999,7 +17703,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 19.61</t>
         </is>
       </c>
     </row>
@@ -17023,24 +17727,24 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G284" t="n">
-        <v>19.61</v>
+        <v>30</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>Bucket on the wrong side was P, should have been N</t>
+          <t>Extra neg- don't count last N trial</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
@@ -17060,7 +17764,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>GO, 19.61</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -17084,7 +17788,7 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -17101,7 +17805,7 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>Extra neg- don't count last N trial</t>
+          <t xml:space="preserve">Says Pos in log but is Neg </t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
@@ -17145,24 +17849,24 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G286" t="n">
-        <v>30</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Says Pos in log but is Neg </t>
+          <t>Says NN in log but is Pos</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
@@ -17182,7 +17886,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 8.87</t>
         </is>
       </c>
     </row>
@@ -17206,24 +17910,24 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>NN</t>
         </is>
       </c>
       <c r="G287" t="n">
-        <v>8.869999999999999</v>
+        <v>30</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>Says NN in log but is Pos</t>
+          <t>Check log</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
@@ -17243,7 +17947,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>GO, 8.87</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -17267,19 +17971,19 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>NN</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G288" t="n">
-        <v>30</v>
+        <v>8.09</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -17304,7 +18008,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 8.09</t>
         </is>
       </c>
     </row>
@@ -17315,20 +18019,20 @@
         </is>
       </c>
       <c r="B289" s="2" t="n">
-        <v>45258</v>
+        <v>45247</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>CBT4</t>
+          <t>CBF3</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>dusty</t>
+          <t>yoshi</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -17336,7 +18040,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>8.09</v>
+        <v>11.13</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -17345,12 +18049,12 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>Check log</t>
+          <t>Ran CBR1 but should be CBF3- so manually check all timings</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-17T04:05:53.213724_dusty_10.0_Test Type 1.log</t>
+          <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
@@ -17365,7 +18069,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>GO, 8.09</t>
+          <t>GO, 11.13</t>
         </is>
       </c>
     </row>
@@ -17389,7 +18093,7 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -17397,7 +18101,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>11.13</v>
+        <v>12.67</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -17406,7 +18110,7 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>Ran CBR1 but should be CBF3- so manually check all timings</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
@@ -17426,7 +18130,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>GO, 11.13</t>
+          <t>GO, 12.67</t>
         </is>
       </c>
     </row>
@@ -17450,7 +18154,7 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -17458,14 +18162,18 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>12.67</v>
+        <v>11.73</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I291" t="inlineStr"/>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J291" t="inlineStr">
         <is>
           <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
@@ -17483,7 +18191,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>GO, 12.67</t>
+          <t>GO, 11.73</t>
         </is>
       </c>
     </row>
@@ -17507,7 +18215,7 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -17515,14 +18223,18 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>11.73</v>
+        <v>14</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I292" t="inlineStr"/>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J292" t="inlineStr">
         <is>
           <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
@@ -17540,7 +18252,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>GO, 11.73</t>
+          <t>GO, 14</t>
         </is>
       </c>
     </row>
@@ -17564,7 +18276,7 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -17572,14 +18284,18 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>14</v>
+        <v>12.4</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I293" t="inlineStr"/>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J293" t="inlineStr">
         <is>
           <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
@@ -17597,7 +18313,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>GO, 14</t>
+          <t>GO, 12.4</t>
         </is>
       </c>
     </row>
@@ -17621,7 +18337,7 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -17629,14 +18345,18 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>12.4</v>
+        <v>12.94</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I294" t="inlineStr"/>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J294" t="inlineStr">
         <is>
           <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
@@ -17654,7 +18374,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>GO, 12.4</t>
+          <t>GO, 12.94</t>
         </is>
       </c>
     </row>
@@ -17678,7 +18398,7 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -17686,14 +18406,18 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>12.94</v>
+        <v>12.37</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I295" t="inlineStr"/>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J295" t="inlineStr">
         <is>
           <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
@@ -17711,7 +18435,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>GO, 12.94</t>
+          <t>GO, 12.37</t>
         </is>
       </c>
     </row>
@@ -17735,7 +18459,7 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -17743,14 +18467,18 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>12.37</v>
+        <v>26.7</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I296" t="inlineStr"/>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J296" t="inlineStr">
         <is>
           <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
@@ -17768,7 +18496,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>GO, 12.37</t>
+          <t>GO, 26.7</t>
         </is>
       </c>
     </row>
@@ -17792,7 +18520,7 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -17800,14 +18528,18 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>26.7</v>
+        <v>16.89</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I297" t="inlineStr"/>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J297" t="inlineStr">
         <is>
           <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
@@ -17825,7 +18557,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>GO, 26.7</t>
+          <t>GO, 16.89</t>
         </is>
       </c>
     </row>
@@ -17849,7 +18581,7 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -17857,14 +18589,18 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>16.89</v>
+        <v>11.99</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="I298" t="inlineStr"/>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J298" t="inlineStr">
         <is>
           <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
@@ -17882,7 +18618,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>GO, 16.89</t>
+          <t>GO, 11.99</t>
         </is>
       </c>
     </row>
@@ -17906,22 +18642,26 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>P</t>
+          <t xml:space="preserve">N </t>
         </is>
       </c>
       <c r="G299" t="n">
-        <v>11.99</v>
+        <v>30</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I299" t="inlineStr"/>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J299" t="inlineStr">
         <is>
           <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
@@ -17939,7 +18679,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>GO, 11.99</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -17963,7 +18703,7 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -17978,7 +18718,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I300" t="inlineStr"/>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J300" t="inlineStr">
         <is>
           <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
@@ -18020,7 +18764,7 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -18035,7 +18779,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I301" t="inlineStr"/>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J301" t="inlineStr">
         <is>
           <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
@@ -18077,7 +18825,7 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -18092,7 +18840,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I302" t="inlineStr"/>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J302" t="inlineStr">
         <is>
           <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
@@ -18134,7 +18886,7 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -18149,7 +18901,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I303" t="inlineStr"/>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J303" t="inlineStr">
         <is>
           <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
@@ -18191,7 +18947,7 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -18206,7 +18962,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I304" t="inlineStr"/>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J304" t="inlineStr">
         <is>
           <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
@@ -18248,7 +19008,7 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -18263,7 +19023,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I305" t="inlineStr"/>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J305" t="inlineStr">
         <is>
           <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
@@ -18305,7 +19069,7 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -18320,7 +19084,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I306" t="inlineStr"/>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J306" t="inlineStr">
         <is>
           <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
@@ -18362,7 +19130,7 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -18377,7 +19145,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I307" t="inlineStr"/>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J307" t="inlineStr">
         <is>
           <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
@@ -18419,7 +19191,7 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -18434,7 +19206,11 @@
           <t>NOGO</t>
         </is>
       </c>
-      <c r="I308" t="inlineStr"/>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J308" t="inlineStr">
         <is>
           <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
@@ -18451,63 +19227,6 @@
         </is>
       </c>
       <c r="M308" t="inlineStr">
-        <is>
-          <t>NOGO, 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>CSU</t>
-        </is>
-      </c>
-      <c r="B309" s="2" t="n">
-        <v>45247</v>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>CBF3</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>yoshi</t>
-        </is>
-      </c>
-      <c r="E309" t="n">
-        <v>20</v>
-      </c>
-      <c r="F309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N </t>
-        </is>
-      </c>
-      <c r="G309" t="n">
-        <v>30</v>
-      </c>
-      <c r="H309" t="inlineStr">
-        <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I309" t="inlineStr"/>
-      <c r="J309" t="inlineStr">
-        <is>
-          <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
-        </is>
-      </c>
-      <c r="K309" t="inlineStr">
-        <is>
-          <t>TrialCBs, ResponseCBs</t>
-        </is>
-      </c>
-      <c r="L309" t="inlineStr">
-        <is>
-          <t>ResponseType, ResponseTime</t>
-        </is>
-      </c>
-      <c r="M309" t="inlineStr">
         <is>
           <t>NOGO, 30</t>
         </is>

--- a/results/CB/Corrections.xlsx
+++ b/results/CB/Corrections.xlsx
@@ -6877,7 +6877,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>, 9.35</t>
+          <t>GO, 9.35</t>
         </is>
       </c>
     </row>
@@ -6943,7 +6943,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Should be NULL ResponseType  - leave blank</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -7004,7 +7004,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Should be NULL ResponseType  - leave blank</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7060,14 +7060,14 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
       <c r="J109" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T04:07:06.316598_gio_4.0_Training randomised Type 2.log</t>
@@ -7085,7 +7085,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>, 8.95</t>
+          <t>GO, 8.95</t>
         </is>
       </c>
     </row>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Should be NULL ResponseType  - leave blank</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7426,14 +7426,14 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
       <c r="J115" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T04:07:06.316598_gio_4.0_Training randomised Type 2.log</t>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>, 9.09</t>
+          <t>GO, 9.09</t>
         </is>
       </c>
     </row>
@@ -7548,14 +7548,14 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
       <c r="J117" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T04:07:06.316598_gio_4.0_Training randomised Type 2.log</t>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>, 9.13</t>
+          <t>GO, 9.13</t>
         </is>
       </c>
     </row>
@@ -8031,14 +8031,12 @@
           <t>NULL</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
+      <c r="G125" t="n">
+        <v>30</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8063,7 +8061,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t xml:space="preserve">, </t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -9626,7 +9624,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9651,7 +9649,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>, 10.93</t>
+          <t>GO, 10.93</t>
         </is>
       </c>
     </row>

--- a/results/CB/Corrections.xlsx
+++ b/results/CB/Corrections.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M308"/>
+  <dimension ref="A1:M307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6938,14 +6938,14 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>Should be NULL ResponseType  - leave blank</t>
-        </is>
-      </c>
       <c r="J107" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T04:07:06.316598_gio_4.0_Training randomised Type 2.log</t>
@@ -6963,7 +6963,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>, 9.15</t>
+          <t>GO, 9.15</t>
         </is>
       </c>
     </row>
@@ -6999,14 +6999,14 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>Should be NULL ResponseType  - leave blank</t>
-        </is>
-      </c>
       <c r="J108" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T04:07:06.316598_gio_4.0_Training randomised Type 2.log</t>
@@ -7024,7 +7024,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>, 9.01</t>
+          <t>GO, 9.01</t>
         </is>
       </c>
     </row>
@@ -7243,14 +7243,14 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>Should be NULL ResponseType  - leave blank</t>
-        </is>
-      </c>
       <c r="J112" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T04:07:06.316598_gio_4.0_Training randomised Type 2.log</t>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>, 8.69</t>
+          <t>GO, 8.69</t>
         </is>
       </c>
     </row>
@@ -8320,40 +8320,38 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>CBR3</t>
+          <t>CBT1</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>yoshi</t>
+          <t>freya</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
+      <c r="G130" t="n">
+        <v>30</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>As per the sheet</t>
+          <t>Windy/rain storm, did not approach first Pos bucket</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-14T19:16:58.918521_yoshi_6.0_Training randomised Type 1.log</t>
+          <t>Experiment_2023-11-14T23:17:57.967289_freya_nan_Test Type 2.log</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -8368,7 +8366,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t xml:space="preserve">, </t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -8379,42 +8377,42 @@
         </is>
       </c>
       <c r="B131" s="2" t="n">
-        <v>45250</v>
+        <v>45251</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>CBT1</t>
+          <t>CBT2</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>freya</t>
+          <t>george</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>NN</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>30</v>
+        <v>15.45</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Windy/rain storm, did not approach first Pos bucket</t>
+          <t>Late button press for GO</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-14T23:17:57.967289_freya_nan_Test Type 2.log</t>
+          <t>Experiment_2023-11-15T02:59:50.231712_george_6.0_Test Type 2.log</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -8429,7 +8427,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 15.45</t>
         </is>
       </c>
     </row>
@@ -8449,19 +8447,19 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>george</t>
+          <t>nix</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>NN</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>15.45</v>
+        <v>10.27</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -8470,12 +8468,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Late button press for GO</t>
+          <t xml:space="preserve"> Errors in test- 7N + 5P</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-15T02:59:50.231712_george_6.0_Test Type 2.log</t>
+          <t>Experiment_2023-11-15T04:42:42.109160_nix_9.0_Test Type 1.log</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -8490,7 +8488,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>GO, 15.45</t>
+          <t>GO, 10.27</t>
         </is>
       </c>
     </row>
@@ -8514,24 +8512,24 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>P</t>
+          <t xml:space="preserve">N </t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>10.27</v>
+        <v>30</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Errors in test- 7N + 5P</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8551,7 +8549,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>GO, 10.27</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -8575,19 +8573,19 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">N </t>
+          <t>M</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>30</v>
+        <v>9.15</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8612,7 +8610,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 9.15</t>
         </is>
       </c>
     </row>
@@ -8636,24 +8634,24 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>M</t>
+          <t xml:space="preserve">N </t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>9.15</v>
+        <v>30</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Meant to be P</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8673,7 +8671,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>GO, 9.15</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -8697,24 +8695,24 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">N </t>
+          <t>P</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>30</v>
+        <v>9.81</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Meant to be P</t>
+          <t>Meant to be N</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8734,7 +8732,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 9.81</t>
         </is>
       </c>
     </row>
@@ -8758,24 +8756,24 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>P</t>
+          <t xml:space="preserve">N </t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>9.81</v>
+        <v>30</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Meant to be N</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -8795,7 +8793,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>GO, 9.81</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -8819,11 +8817,11 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">N </t>
+          <t>N</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -8836,7 +8834,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Meant to be NP</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -8880,24 +8878,24 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>30</v>
+        <v>9.74</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Meant to be NP</t>
+          <t>meant to be P</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -8917,7 +8915,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 9.74</t>
         </is>
       </c>
     </row>
@@ -8941,15 +8939,15 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>9.74</v>
+        <v>15.25</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -8958,7 +8956,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>meant to be P</t>
+          <t>Meant to be P</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -8978,7 +8976,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>GO, 9.74</t>
+          <t>GO, 15.25</t>
         </is>
       </c>
     </row>
@@ -9002,24 +9000,24 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>15.25</v>
+        <v>30</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Meant to be P</t>
+          <t>meant to be P</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -9039,7 +9037,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>GO, 15.25</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -9063,24 +9061,24 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>30</v>
+        <v>11.53</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>meant to be P</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -9100,7 +9098,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 11.53</t>
         </is>
       </c>
     </row>
@@ -9124,15 +9122,15 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>11.53</v>
+        <v>24.2</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -9161,7 +9159,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>GO, 11.53</t>
+          <t>GO, 24.2</t>
         </is>
       </c>
     </row>
@@ -9185,19 +9183,19 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>NN</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>24.2</v>
+        <v>30</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9222,7 +9220,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>GO, 24.2</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -9246,19 +9244,19 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>NN</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>30</v>
+        <v>11.09</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9283,7 +9281,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 11.09</t>
         </is>
       </c>
     </row>
@@ -9307,19 +9305,19 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>11.09</v>
+        <v>30</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9344,7 +9342,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>GO, 11.09</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -9364,33 +9362,33 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>nix</t>
+          <t>gio</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>30</v>
+        <v>10.12</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Pos bucket on wrong side- late Go response due to wrong bucket side</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-15T04:42:42.109160_nix_9.0_Test Type 1.log</t>
+          <t>Experiment_2023-11-15T05:22:53.513691_gio_6.0_Test Type 2.log</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -9405,7 +9403,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 10.12</t>
         </is>
       </c>
     </row>
@@ -9429,7 +9427,7 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -9437,7 +9435,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>10.12</v>
+        <v>9.49</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -9446,7 +9444,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Pos bucket on wrong side- late Go response due to wrong bucket side</t>
+          <t>Go button pressed too early</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -9466,7 +9464,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>GO, 10.12</t>
+          <t>GO, 9.49</t>
         </is>
       </c>
     </row>
@@ -9477,7 +9475,7 @@
         </is>
       </c>
       <c r="B149" s="2" t="n">
-        <v>45251</v>
+        <v>45252</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -9486,19 +9484,19 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>gio</t>
+          <t>smudge</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>9.49</v>
+        <v>29.46</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -9507,12 +9505,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Go button pressed too early</t>
+          <t>Just timed out on Neg bucket for NoGo- check vid</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-15T05:22:53.513691_gio_6.0_Test Type 2.log</t>
+          <t>Experiment_2023-11-15T16:42:36.211643_smudge_8.0_Test Type 2.log</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -9527,7 +9525,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>GO, 9.49</t>
+          <t>GO, 29.46</t>
         </is>
       </c>
     </row>
@@ -9538,7 +9536,7 @@
         </is>
       </c>
       <c r="B150" s="2" t="n">
-        <v>45252</v>
+        <v>45253</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -9547,19 +9545,19 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>smudge</t>
+          <t>yoshi</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G150" t="n">
-        <v>29.46</v>
+        <v>10.93</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -9568,12 +9566,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Just timed out on Neg bucket for NoGo- check vid</t>
+          <t>Early horse release before button not pressed</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-15T16:42:36.211643_smudge_8.0_Test Type 2.log</t>
+          <t>Experiment_2023-11-15T18:35:59.371714_yoshi_9.0_Test Type 2.log</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -9588,7 +9586,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>GO, 29.46</t>
+          <t>GO, 10.93</t>
         </is>
       </c>
     </row>
@@ -9608,11 +9606,11 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>yoshi</t>
+          <t>clover</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -9620,7 +9618,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>10.93</v>
+        <v>11.85</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -9629,12 +9627,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Early horse release before button not pressed</t>
+          <t>Errors in test at trial 11 a N was run instead of a P.  An extra trial was added so horse did 16 trials</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-15T18:35:59.371714_yoshi_9.0_Test Type 2.log</t>
+          <t>Experiment_2023-11-15T23:18:27.463685_clover_nan_Test Type 2.log</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -9649,7 +9647,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>GO, 10.93</t>
+          <t>GO, 11.85</t>
         </is>
       </c>
     </row>
@@ -9673,15 +9671,15 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G152" t="n">
-        <v>11.85</v>
+        <v>18.88</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -9690,7 +9688,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Errors in test at trial 11 a N was run instead of a P.  An extra trial was added so horse did 16 trials</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9710,7 +9708,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>GO, 11.85</t>
+          <t>GO, 18.88</t>
         </is>
       </c>
     </row>
@@ -9734,19 +9732,19 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G153" t="n">
-        <v>18.88</v>
+        <v>30</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9771,7 +9769,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>GO, 18.88</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -9795,19 +9793,19 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G154" t="n">
-        <v>30</v>
+        <v>10.94</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9832,7 +9830,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 10.94</t>
         </is>
       </c>
     </row>
@@ -9856,19 +9854,19 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G155" t="n">
-        <v>10.94</v>
+        <v>30</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9893,7 +9891,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>GO, 10.94</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -9917,7 +9915,7 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -9978,11 +9976,11 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -10039,19 +10037,19 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G158" t="n">
-        <v>30</v>
+        <v>11.93</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10076,7 +10074,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 11.93</t>
         </is>
       </c>
     </row>
@@ -10100,19 +10098,19 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G159" t="n">
-        <v>11.93</v>
+        <v>30</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10137,7 +10135,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>GO, 11.93</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -10161,19 +10159,19 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G160" t="n">
-        <v>30</v>
+        <v>10.48</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10198,7 +10196,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 10.48</t>
         </is>
       </c>
     </row>
@@ -10222,7 +10220,7 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -10230,7 +10228,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>10.48</v>
+        <v>12.67</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -10239,7 +10237,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t xml:space="preserve">Was run as N, then repeated so horse did extra 11 (P). </t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -10259,7 +10257,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>GO, 10.48</t>
+          <t>GO, 12.67</t>
         </is>
       </c>
     </row>
@@ -10283,24 +10281,24 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G162" t="n">
-        <v>12.67</v>
+        <v>30</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Was run as N, then repeated so horse did extra 11 (P). </t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -10320,7 +10318,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>GO, 12.67</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -10344,11 +10342,11 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>NN</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -10405,19 +10403,19 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>NN</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G164" t="n">
-        <v>30</v>
+        <v>12.8</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10442,7 +10440,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 12.8</t>
         </is>
       </c>
     </row>
@@ -10466,19 +10464,19 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G165" t="n">
-        <v>12.8</v>
+        <v>30</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10503,7 +10501,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>GO, 12.8</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -10514,42 +10512,42 @@
         </is>
       </c>
       <c r="B166" s="2" t="n">
-        <v>45253</v>
+        <v>45255</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>CBT2</t>
+          <t>CBT3</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>clover</t>
+          <t>nix</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G166" t="n">
-        <v>30</v>
+        <v>10.01</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Bucket on the wrong side</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-15T23:18:27.463685_clover_nan_Test Type 2.log</t>
+          <t>Experiment_2023-11-16T09:12:31.465402_nix_10.0_Test Type 3.log</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -10564,7 +10562,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 10.01</t>
         </is>
       </c>
     </row>
@@ -10588,24 +10586,24 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G167" t="n">
-        <v>10.01</v>
+        <v>30</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Bucket on the wrong side</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -10625,7 +10623,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>GO, 10.01</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -10649,19 +10647,19 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G168" t="n">
-        <v>30</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10686,7 +10684,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 9.8</t>
         </is>
       </c>
     </row>
@@ -10710,15 +10708,15 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G169" t="n">
-        <v>9.800000000000001</v>
+        <v>20.87</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -10747,7 +10745,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>GO, 9.8</t>
+          <t>GO, 20.87</t>
         </is>
       </c>
     </row>
@@ -10771,15 +10769,15 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G170" t="n">
-        <v>20.87</v>
+        <v>9.35</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -10808,7 +10806,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>GO, 20.87</t>
+          <t>GO, 9.35</t>
         </is>
       </c>
     </row>
@@ -10832,15 +10830,15 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G171" t="n">
-        <v>9.35</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -10869,7 +10867,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>GO, 9.35</t>
+          <t>GO, 8.95</t>
         </is>
       </c>
     </row>
@@ -10893,7 +10891,7 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -10901,7 +10899,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>8.949999999999999</v>
+        <v>10.57</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -10910,7 +10908,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Two buckets- check video</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -10930,7 +10928,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>GO, 8.95</t>
+          <t>GO, 10.57</t>
         </is>
       </c>
     </row>
@@ -10954,24 +10952,24 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G173" t="n">
-        <v>10.57</v>
+        <v>30</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Two buckets- check video</t>
+          <t>Two buckets (extra trial?)</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -10991,7 +10989,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>GO, 10.57</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -11015,24 +11013,24 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G174" t="n">
-        <v>30</v>
+        <v>9.48</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Two buckets (extra trial?)</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -11052,7 +11050,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 9.48</t>
         </is>
       </c>
     </row>
@@ -11076,15 +11074,15 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G175" t="n">
-        <v>9.48</v>
+        <v>11.14</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -11113,7 +11111,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>GO, 9.48</t>
+          <t>GO, 11.14</t>
         </is>
       </c>
     </row>
@@ -11137,19 +11135,19 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G176" t="n">
-        <v>11.14</v>
+        <v>30</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11174,7 +11172,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>GO, 11.14</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -11198,7 +11196,7 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -11206,11 +11204,11 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>30</v>
+        <v>13.46</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11235,7 +11233,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 13.46</t>
         </is>
       </c>
     </row>
@@ -11259,15 +11257,15 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G178" t="n">
-        <v>13.46</v>
+        <v>8.49</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -11296,7 +11294,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>GO, 13.46</t>
+          <t>GO, 8.49</t>
         </is>
       </c>
     </row>
@@ -11320,24 +11318,24 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>NN</t>
         </is>
       </c>
       <c r="G179" t="n">
-        <v>8.49</v>
+        <v>30</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Did not touch. Bucket</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -11357,7 +11355,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>GO, 8.49</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -11381,11 +11379,11 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>NN</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -11398,7 +11396,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Did not touch. Bucket</t>
+          <t>Early horse release before button not pressed</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -11429,11 +11427,11 @@
         </is>
       </c>
       <c r="B181" s="2" t="n">
-        <v>45255</v>
+        <v>45256</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>CBT3</t>
+          <t>CBT4</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -11442,29 +11440,29 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G181" t="n">
-        <v>30</v>
+        <v>11.01</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Early horse release before button not pressed</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-16T09:12:31.465402_nix_10.0_Test Type 3.log</t>
+          <t>Experiment_2023-11-16T15:46:42.899255_nix_11.0_Test Type 1.log</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -11479,7 +11477,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 11.01</t>
         </is>
       </c>
     </row>
@@ -11503,15 +11501,15 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G182" t="n">
-        <v>11.01</v>
+        <v>12.99</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -11520,7 +11518,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Late button press for GO</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -11540,7 +11538,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>GO, 11.01</t>
+          <t>GO, 12.99</t>
         </is>
       </c>
     </row>
@@ -11564,15 +11562,15 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G183" t="n">
-        <v>12.99</v>
+        <v>10.07</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -11581,7 +11579,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Late button press for GO</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -11601,7 +11599,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>GO, 12.99</t>
+          <t>GO, 10.07</t>
         </is>
       </c>
     </row>
@@ -11625,15 +11623,15 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G184" t="n">
-        <v>10.07</v>
+        <v>12.67</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -11642,7 +11640,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t xml:space="preserve">No button press- Go resp is criterion- check vids </t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -11662,7 +11660,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>GO, 10.07</t>
+          <t>GO, 12.67</t>
         </is>
       </c>
     </row>
@@ -11686,15 +11684,15 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G185" t="n">
-        <v>12.67</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -11703,7 +11701,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">No button press- Go resp is criterion- check vids </t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -11723,7 +11721,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>GO, 12.67</t>
+          <t>GO, 9.87</t>
         </is>
       </c>
     </row>
@@ -11747,7 +11745,7 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -11755,7 +11753,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>9.869999999999999</v>
+        <v>12.41</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -11784,7 +11782,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>GO, 9.87</t>
+          <t>GO, 12.41</t>
         </is>
       </c>
     </row>
@@ -11808,19 +11806,19 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G187" t="n">
-        <v>12.41</v>
+        <v>30</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11845,7 +11843,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>GO, 12.41</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -11869,19 +11867,19 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G188" t="n">
-        <v>30</v>
+        <v>11.2</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11906,7 +11904,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 11.2</t>
         </is>
       </c>
     </row>
@@ -11930,15 +11928,15 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G189" t="n">
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -11967,7 +11965,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>GO, 11.2</t>
+          <t>GO, 10.4</t>
         </is>
       </c>
     </row>
@@ -11991,19 +11989,19 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G190" t="n">
-        <v>10.4</v>
+        <v>30</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12028,7 +12026,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>GO, 10.4</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -12052,7 +12050,7 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -12113,19 +12111,19 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G192" t="n">
-        <v>30</v>
+        <v>10.2</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12150,7 +12148,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 10.2</t>
         </is>
       </c>
     </row>
@@ -12174,19 +12172,19 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>NN</t>
         </is>
       </c>
       <c r="G193" t="n">
-        <v>10.2</v>
+        <v>30</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12211,7 +12209,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>GO, 10.2</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -12235,19 +12233,19 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>NN</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G194" t="n">
-        <v>30</v>
+        <v>11.39</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12272,7 +12270,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 11.39</t>
         </is>
       </c>
     </row>
@@ -12296,19 +12294,19 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G195" t="n">
-        <v>11.39</v>
+        <v>30</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12333,7 +12331,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>GO, 11.39</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -12353,33 +12351,33 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>nix</t>
+          <t>gio</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G196" t="n">
-        <v>30</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>2 Log files, computer stopped after trial 3 Median- Restart trial 4?</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-16T15:46:42.899255_nix_11.0_Test Type 1.log</t>
+          <t>Experiment_2023-11-16T17:55:24.333022_gio_9.0_Test Type 1.log</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -12394,7 +12392,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 9.29</t>
         </is>
       </c>
     </row>
@@ -12418,24 +12416,24 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G197" t="n">
-        <v>9.289999999999999</v>
+        <v>30</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>2 Log files, computer stopped after trial 3 Median- Restart trial 4?</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -12455,7 +12453,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>GO, 9.29</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -12479,19 +12477,19 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G198" t="n">
-        <v>30</v>
+        <v>10.36</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12516,7 +12514,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 10.36</t>
         </is>
       </c>
     </row>
@@ -12540,19 +12538,19 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G199" t="n">
-        <v>10.36</v>
+        <v>30</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12577,7 +12575,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>GO, 10.36</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -12601,19 +12599,19 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G200" t="n">
-        <v>30</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12638,7 +12636,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 9.87</t>
         </is>
       </c>
     </row>
@@ -12662,7 +12660,7 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -12670,7 +12668,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>9.869999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -12699,7 +12697,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>GO, 9.87</t>
+          <t>GO, 9.33</t>
         </is>
       </c>
     </row>
@@ -12723,19 +12721,19 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G202" t="n">
-        <v>9.33</v>
+        <v>30</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12760,7 +12758,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>GO, 9.33</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -12784,19 +12782,19 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G203" t="n">
-        <v>30</v>
+        <v>8.76</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12821,7 +12819,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 8.76</t>
         </is>
       </c>
     </row>
@@ -12845,15 +12843,15 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G204" t="n">
-        <v>8.76</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -12882,7 +12880,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>GO, 8.76</t>
+          <t>GO, 9.22</t>
         </is>
       </c>
     </row>
@@ -12906,19 +12904,19 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G205" t="n">
-        <v>9.220000000000001</v>
+        <v>30</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12943,7 +12941,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>GO, 9.22</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -12967,7 +12965,7 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -13028,19 +13026,19 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G207" t="n">
-        <v>30</v>
+        <v>9.43</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13065,7 +13063,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 9.43</t>
         </is>
       </c>
     </row>
@@ -13089,19 +13087,19 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>NN</t>
         </is>
       </c>
       <c r="G208" t="n">
-        <v>9.43</v>
+        <v>30</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13126,7 +13124,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>GO, 9.43</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -13150,19 +13148,19 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>NN</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G209" t="n">
-        <v>30</v>
+        <v>9.66</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13187,7 +13185,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 9.66</t>
         </is>
       </c>
     </row>
@@ -13211,19 +13209,19 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G210" t="n">
-        <v>9.66</v>
+        <v>30</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13248,7 +13246,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>GO, 9.66</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -13259,7 +13257,7 @@
         </is>
       </c>
       <c r="B211" s="2" t="n">
-        <v>45256</v>
+        <v>45257</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -13268,11 +13266,11 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>gio</t>
+          <t>jelly</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -13280,21 +13278,21 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>30</v>
+        <v>27.17</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t xml:space="preserve">Go response but not captured </t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-16T17:55:24.333022_gio_9.0_Test Type 1.log</t>
+          <t>Experiment_2023-11-16T19:24:59.492473_jelly_9.0_Test Type 1.log</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -13309,7 +13307,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 27.17</t>
         </is>
       </c>
     </row>
@@ -13333,15 +13331,15 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G212" t="n">
-        <v>27.17</v>
+        <v>11.2</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -13350,7 +13348,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Go response but not captured </t>
+          <t>late button press for GO due to broken robot</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -13370,7 +13368,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>GO, 27.17</t>
+          <t>GO, 11.2</t>
         </is>
       </c>
     </row>
@@ -13390,19 +13388,19 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>jelly</t>
+          <t>smudge</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G213" t="n">
-        <v>11.2</v>
+        <v>10.14</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -13411,12 +13409,12 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>late button press for GO due to broken robot</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-16T19:24:59.492473_jelly_9.0_Test Type 1.log</t>
+          <t>Experiment_2023-11-16T20:27:00.214523_smudge_10.0_Test Type 1.log</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -13431,7 +13429,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>GO, 11.2</t>
+          <t>GO, 10.14</t>
         </is>
       </c>
     </row>
@@ -13455,19 +13453,19 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G214" t="n">
-        <v>10.14</v>
+        <v>30</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13492,7 +13490,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>GO, 10.14</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -13516,24 +13514,24 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G215" t="n">
-        <v>30</v>
+        <v>10.79</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t xml:space="preserve">Go response but not captured </t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -13553,7 +13551,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 10.79</t>
         </is>
       </c>
     </row>
@@ -13577,24 +13575,24 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G216" t="n">
-        <v>10.79</v>
+        <v>30</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Go response but not captured </t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -13614,7 +13612,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>GO, 10.79</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -13638,19 +13636,19 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G217" t="n">
-        <v>30</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13675,7 +13673,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 9.87</t>
         </is>
       </c>
     </row>
@@ -13699,7 +13697,7 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -13707,7 +13705,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>9.869999999999999</v>
+        <v>10.87</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -13736,7 +13734,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>GO, 9.87</t>
+          <t>GO, 10.87</t>
         </is>
       </c>
     </row>
@@ -13760,24 +13758,24 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G219" t="n">
-        <v>10.87</v>
+        <v>30</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>NoGo response when should be Go response</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -13797,7 +13795,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>GO, 10.87</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -13821,24 +13819,24 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G220" t="n">
-        <v>30</v>
+        <v>10.13</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>NoGo response when should be Go response</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -13858,7 +13856,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 10.13</t>
         </is>
       </c>
     </row>
@@ -13882,15 +13880,15 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G221" t="n">
-        <v>10.13</v>
+        <v>10.22</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -13919,7 +13917,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>GO, 10.13</t>
+          <t>GO, 10.22</t>
         </is>
       </c>
     </row>
@@ -13943,19 +13941,19 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G222" t="n">
-        <v>10.22</v>
+        <v>30</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -13980,7 +13978,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>GO, 10.22</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -14004,7 +14002,7 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -14065,24 +14063,24 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G224" t="n">
-        <v>30</v>
+        <v>10.87</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Video and log don't match but NoGO is criterion</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -14102,7 +14100,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 10.87</t>
         </is>
       </c>
     </row>
@@ -14126,24 +14124,24 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>NN</t>
         </is>
       </c>
       <c r="G225" t="n">
-        <v>10.87</v>
+        <v>30</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Video and log don't match but NoGO is criterion</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -14163,7 +14161,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>GO, 10.87</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -14187,19 +14185,19 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>NN</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G226" t="n">
-        <v>30</v>
+        <v>10.87</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14224,7 +14222,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 10.87</t>
         </is>
       </c>
     </row>
@@ -14248,19 +14246,19 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G227" t="n">
-        <v>10.87</v>
+        <v>30</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14285,7 +14283,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>GO, 10.87</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -14300,28 +14298,28 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>CBT4</t>
+          <t>CBT3</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>smudge</t>
+          <t>myrtle</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G228" t="n">
-        <v>30</v>
+        <v>7.99</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14331,7 +14329,7 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-16T20:27:00.214523_smudge_10.0_Test Type 1.log</t>
+          <t>Experiment_2023-11-16T21:17:46.006067_myrtle_10.0_Test Type 3.log</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -14346,7 +14344,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 7.99</t>
         </is>
       </c>
     </row>
@@ -14370,24 +14368,24 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G229" t="n">
-        <v>7.99</v>
+        <v>30</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Go response triggered but NoGo</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -14407,7 +14405,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>GO, 7.99</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -14431,24 +14429,24 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G230" t="n">
-        <v>30</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Go response triggered but NoGo</t>
+          <t>NoGo response when should be Go response</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -14468,7 +14466,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 9.14</t>
         </is>
       </c>
     </row>
@@ -14492,15 +14490,15 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G231" t="n">
-        <v>9.140000000000001</v>
+        <v>18.01</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -14509,7 +14507,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>NoGo response when should be Go response</t>
+          <t>OK on log-Nogo</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -14529,7 +14527,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>GO, 9.14</t>
+          <t>GO, 18.01</t>
         </is>
       </c>
     </row>
@@ -14553,15 +14551,15 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G232" t="n">
-        <v>18.01</v>
+        <v>10.56</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -14570,7 +14568,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>OK on log-Nogo</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -14590,7 +14588,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>GO, 18.01</t>
+          <t>GO, 10.56</t>
         </is>
       </c>
     </row>
@@ -14614,15 +14612,15 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G233" t="n">
-        <v>10.56</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -14631,7 +14629,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Button pressed late?</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -14651,7 +14649,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>GO, 10.56</t>
+          <t>GO, 9.22</t>
         </is>
       </c>
     </row>
@@ -14675,7 +14673,7 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -14683,7 +14681,7 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>9.220000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -14692,7 +14690,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>Button pressed late?</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -14712,7 +14710,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>GO, 9.22</t>
+          <t>GO, 9.55</t>
         </is>
       </c>
     </row>
@@ -14736,19 +14734,19 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G235" t="n">
-        <v>9.550000000000001</v>
+        <v>30</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -14773,7 +14771,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>GO, 9.55</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -14797,11 +14795,11 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -14858,19 +14856,19 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G237" t="n">
-        <v>30</v>
+        <v>10.13</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -14895,7 +14893,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 10.13</t>
         </is>
       </c>
     </row>
@@ -14919,19 +14917,19 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G238" t="n">
-        <v>10.13</v>
+        <v>30</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -14956,7 +14954,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>GO, 10.13</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -14980,7 +14978,7 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -15041,24 +15039,24 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G240" t="n">
-        <v>30</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>OK on log-Nogo</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -15078,7 +15076,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 9.63</t>
         </is>
       </c>
     </row>
@@ -15102,24 +15100,24 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>NN</t>
         </is>
       </c>
       <c r="G241" t="n">
-        <v>9.630000000000001</v>
+        <v>30</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>OK on log-Nogo</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -15139,7 +15137,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>GO, 9.63</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -15163,11 +15161,11 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>NN</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -15220,33 +15218,33 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>myrtle</t>
+          <t>yoshi</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G243" t="n">
-        <v>30</v>
+        <v>8.23</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Late button press for GO</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-16T21:17:46.006067_myrtle_10.0_Test Type 3.log</t>
+          <t>Experiment_2023-11-16T22:01:25.798273_yoshi_10.0_Test Type 3.log</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -15261,7 +15259,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 8.23</t>
         </is>
       </c>
     </row>
@@ -15285,15 +15283,15 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G244" t="n">
-        <v>8.23</v>
+        <v>25.39</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -15302,7 +15300,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Late button press for GO</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -15322,7 +15320,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>GO, 8.23</t>
+          <t>GO, 25.39</t>
         </is>
       </c>
     </row>
@@ -15346,15 +15344,15 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G245" t="n">
-        <v>25.39</v>
+        <v>8.16</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -15383,7 +15381,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>GO, 25.39</t>
+          <t>GO, 8.16</t>
         </is>
       </c>
     </row>
@@ -15407,19 +15405,19 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G246" t="n">
-        <v>8.16</v>
+        <v>30</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15444,7 +15442,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>GO, 8.16</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -15468,19 +15466,19 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G247" t="n">
-        <v>30</v>
+        <v>9.48</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15505,7 +15503,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 9.48</t>
         </is>
       </c>
     </row>
@@ -15529,15 +15527,15 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G248" t="n">
-        <v>9.48</v>
+        <v>8.82</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -15566,7 +15564,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>GO, 9.48</t>
+          <t>GO, 8.82</t>
         </is>
       </c>
     </row>
@@ -15590,7 +15588,7 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -15598,7 +15596,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>8.82</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -15627,7 +15625,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>GO, 8.82</t>
+          <t>GO, 9.14</t>
         </is>
       </c>
     </row>
@@ -15651,19 +15649,19 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G250" t="n">
-        <v>9.140000000000001</v>
+        <v>30</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15688,7 +15686,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>GO, 9.14</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -15712,19 +15710,19 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G251" t="n">
-        <v>30</v>
+        <v>8.6</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15749,7 +15747,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 8.6</t>
         </is>
       </c>
     </row>
@@ -15773,15 +15771,15 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G252" t="n">
-        <v>8.6</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -15810,7 +15808,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>GO, 8.6</t>
+          <t>GO, 8.95</t>
         </is>
       </c>
     </row>
@@ -15834,19 +15832,19 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G253" t="n">
-        <v>8.949999999999999</v>
+        <v>30</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -15871,7 +15869,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>GO, 8.95</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -15895,7 +15893,7 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -15956,19 +15954,19 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>30</v>
+        <v>9.08</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -15993,7 +15991,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 9.08</t>
         </is>
       </c>
     </row>
@@ -16017,19 +16015,19 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>NN</t>
         </is>
       </c>
       <c r="G256" t="n">
-        <v>9.08</v>
+        <v>30</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16054,7 +16052,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>GO, 9.08</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -16078,11 +16076,11 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>NN</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -16135,23 +16133,23 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>yoshi</t>
+          <t>dusty</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G258" t="n">
-        <v>30</v>
+        <v>7.62</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16161,7 +16159,7 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-16T22:01:25.798273_yoshi_10.0_Test Type 3.log</t>
+          <t>Experiment_2023-11-16T23:55:33.357304_dusty_9.0_Test Type 3.log</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -16176,7 +16174,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 7.62</t>
         </is>
       </c>
     </row>
@@ -16200,15 +16198,15 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G259" t="n">
-        <v>7.62</v>
+        <v>15.96</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -16237,7 +16235,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>GO, 7.62</t>
+          <t>GO, 15.96</t>
         </is>
       </c>
     </row>
@@ -16261,15 +16259,15 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G260" t="n">
-        <v>15.96</v>
+        <v>8.56</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -16298,7 +16296,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>GO, 15.96</t>
+          <t>GO, 8.56</t>
         </is>
       </c>
     </row>
@@ -16322,15 +16320,15 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G261" t="n">
-        <v>8.56</v>
+        <v>11.54</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -16359,7 +16357,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>GO, 8.56</t>
+          <t>GO, 11.54</t>
         </is>
       </c>
     </row>
@@ -16383,19 +16381,19 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G262" t="n">
-        <v>11.54</v>
+        <v>30</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16420,7 +16418,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>GO, 11.54</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -16444,11 +16442,11 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -16505,7 +16503,7 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -16513,11 +16511,11 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>30</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -16542,7 +16540,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 8.61</t>
         </is>
       </c>
     </row>
@@ -16566,19 +16564,19 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G265" t="n">
-        <v>8.609999999999999</v>
+        <v>30</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -16603,7 +16601,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>GO, 8.61</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -16627,11 +16625,11 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -16688,19 +16686,19 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G267" t="n">
-        <v>30</v>
+        <v>9.6</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16725,7 +16723,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 9.6</t>
         </is>
       </c>
     </row>
@@ -16749,19 +16747,19 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G268" t="n">
-        <v>9.6</v>
+        <v>30</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -16786,7 +16784,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>GO, 9.6</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -16810,7 +16808,7 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -16871,19 +16869,19 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G270" t="n">
-        <v>30</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -16908,7 +16906,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 8.46</t>
         </is>
       </c>
     </row>
@@ -16932,19 +16930,19 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>NN</t>
         </is>
       </c>
       <c r="G271" t="n">
-        <v>8.460000000000001</v>
+        <v>30</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -16969,7 +16967,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>GO, 8.46</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -16993,11 +16991,11 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>NN</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -17041,11 +17039,11 @@
         </is>
       </c>
       <c r="B273" s="2" t="n">
-        <v>45257</v>
+        <v>45258</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>CBT3</t>
+          <t>CBT4</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -17054,19 +17052,19 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G273" t="n">
-        <v>30</v>
+        <v>10.12</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -17076,7 +17074,7 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-16T23:55:33.357304_dusty_9.0_Test Type 3.log</t>
+          <t>Experiment_2023-11-17T04:05:53.213724_dusty_10.0_Test Type 1.log</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
@@ -17091,7 +17089,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 10.12</t>
         </is>
       </c>
     </row>
@@ -17115,15 +17113,15 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G274" t="n">
-        <v>10.12</v>
+        <v>19.18</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -17152,7 +17150,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>GO, 10.12</t>
+          <t>GO, 19.18</t>
         </is>
       </c>
     </row>
@@ -17176,19 +17174,19 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G275" t="n">
-        <v>19.18</v>
+        <v>30</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17213,7 +17211,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>GO, 19.18</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -17237,11 +17235,11 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -17298,19 +17296,19 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G277" t="n">
-        <v>30</v>
+        <v>9.92</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -17335,7 +17333,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 9.92</t>
         </is>
       </c>
     </row>
@@ -17359,7 +17357,7 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -17367,7 +17365,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>9.92</v>
+        <v>9.49</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -17396,7 +17394,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>GO, 9.92</t>
+          <t>GO, 9.49</t>
         </is>
       </c>
     </row>
@@ -17420,19 +17418,19 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G279" t="n">
-        <v>9.49</v>
+        <v>30</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -17457,7 +17455,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>GO, 9.49</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -17481,11 +17479,11 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -17542,11 +17540,11 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -17559,7 +17557,7 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Bucket on the wrong side- was N, should have been P</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
@@ -17603,24 +17601,24 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G282" t="n">
-        <v>30</v>
+        <v>19.61</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>Bucket on the wrong side- was N, should have been P</t>
+          <t>Bucket on the wrong side was P, should have been N</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
@@ -17640,7 +17638,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 19.61</t>
         </is>
       </c>
     </row>
@@ -17664,24 +17662,24 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G283" t="n">
-        <v>19.61</v>
+        <v>30</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>Bucket on the wrong side was P, should have been N</t>
+          <t>Extra neg- don't count last N trial</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
@@ -17701,7 +17699,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>GO, 19.61</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -17725,7 +17723,7 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -17742,7 +17740,7 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>Extra neg- don't count last N trial</t>
+          <t xml:space="preserve">Says Pos in log but is Neg </t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
@@ -17786,24 +17784,24 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G285" t="n">
-        <v>30</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Says Pos in log but is Neg </t>
+          <t>Says NN in log but is Pos</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
@@ -17823,7 +17821,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 8.87</t>
         </is>
       </c>
     </row>
@@ -17847,24 +17845,24 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>NN</t>
         </is>
       </c>
       <c r="G286" t="n">
-        <v>8.869999999999999</v>
+        <v>30</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>Says NN in log but is Pos</t>
+          <t>Check log</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
@@ -17884,7 +17882,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>GO, 8.87</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -17908,19 +17906,19 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>NN</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G287" t="n">
-        <v>30</v>
+        <v>8.09</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -17945,7 +17943,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 8.09</t>
         </is>
       </c>
     </row>
@@ -17956,20 +17954,20 @@
         </is>
       </c>
       <c r="B288" s="2" t="n">
-        <v>45258</v>
+        <v>45247</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>CBT4</t>
+          <t>CBF3</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>dusty</t>
+          <t>yoshi</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -17977,7 +17975,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>8.09</v>
+        <v>11.13</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -17986,12 +17984,12 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>Check log</t>
+          <t>Ran CBR1 but should be CBF3- so manually check all timings</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-17T04:05:53.213724_dusty_10.0_Test Type 1.log</t>
+          <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
@@ -18006,7 +18004,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>GO, 8.09</t>
+          <t>GO, 11.13</t>
         </is>
       </c>
     </row>
@@ -18030,7 +18028,7 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -18038,7 +18036,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>11.13</v>
+        <v>12.67</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -18047,7 +18045,7 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>Ran CBR1 but should be CBF3- so manually check all timings</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
@@ -18067,7 +18065,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>GO, 11.13</t>
+          <t>GO, 12.67</t>
         </is>
       </c>
     </row>
@@ -18091,7 +18089,7 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -18099,7 +18097,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>12.67</v>
+        <v>11.73</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -18128,7 +18126,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>GO, 12.67</t>
+          <t>GO, 11.73</t>
         </is>
       </c>
     </row>
@@ -18152,7 +18150,7 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -18160,7 +18158,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>11.73</v>
+        <v>14</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -18189,7 +18187,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>GO, 11.73</t>
+          <t>GO, 14</t>
         </is>
       </c>
     </row>
@@ -18213,7 +18211,7 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -18221,7 +18219,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>14</v>
+        <v>12.4</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -18250,7 +18248,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>GO, 14</t>
+          <t>GO, 12.4</t>
         </is>
       </c>
     </row>
@@ -18274,7 +18272,7 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -18282,7 +18280,7 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>12.4</v>
+        <v>12.94</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -18311,7 +18309,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>GO, 12.4</t>
+          <t>GO, 12.94</t>
         </is>
       </c>
     </row>
@@ -18335,7 +18333,7 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -18343,7 +18341,7 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>12.94</v>
+        <v>12.37</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -18372,7 +18370,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>GO, 12.94</t>
+          <t>GO, 12.37</t>
         </is>
       </c>
     </row>
@@ -18396,7 +18394,7 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -18404,7 +18402,7 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>12.37</v>
+        <v>26.7</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -18433,7 +18431,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>GO, 12.37</t>
+          <t>GO, 26.7</t>
         </is>
       </c>
     </row>
@@ -18457,7 +18455,7 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -18465,7 +18463,7 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>26.7</v>
+        <v>16.89</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -18494,7 +18492,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>GO, 26.7</t>
+          <t>GO, 16.89</t>
         </is>
       </c>
     </row>
@@ -18518,7 +18516,7 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -18526,7 +18524,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>16.89</v>
+        <v>11.99</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -18555,7 +18553,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>GO, 16.89</t>
+          <t>GO, 11.99</t>
         </is>
       </c>
     </row>
@@ -18579,19 +18577,19 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>P</t>
+          <t xml:space="preserve">N </t>
         </is>
       </c>
       <c r="G298" t="n">
-        <v>11.99</v>
+        <v>30</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -18616,7 +18614,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>GO, 11.99</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
     </row>
@@ -18640,7 +18638,7 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -18701,7 +18699,7 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -18762,7 +18760,7 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -18823,7 +18821,7 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -18884,7 +18882,7 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -18945,7 +18943,7 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -19006,7 +19004,7 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -19067,7 +19065,7 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -19128,7 +19126,7 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -19164,67 +19162,6 @@
         </is>
       </c>
       <c r="M307" t="inlineStr">
-        <is>
-          <t>NOGO, 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>CSU</t>
-        </is>
-      </c>
-      <c r="B308" s="2" t="n">
-        <v>45247</v>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>CBF3</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>yoshi</t>
-        </is>
-      </c>
-      <c r="E308" t="n">
-        <v>20</v>
-      </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N </t>
-        </is>
-      </c>
-      <c r="G308" t="n">
-        <v>30</v>
-      </c>
-      <c r="H308" t="inlineStr">
-        <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I308" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="J308" t="inlineStr">
-        <is>
-          <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
-        </is>
-      </c>
-      <c r="K308" t="inlineStr">
-        <is>
-          <t>TrialCBs, ResponseCBs</t>
-        </is>
-      </c>
-      <c r="L308" t="inlineStr">
-        <is>
-          <t>ResponseType, ResponseTime</t>
-        </is>
-      </c>
-      <c r="M308" t="inlineStr">
         <is>
           <t>NOGO, 30</t>
         </is>
